--- a/output/Data and Chart Outputs/switzerland_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/switzerland_power_capacity_monthly.xlsx
@@ -24,8 +24,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -65,12 +65,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1006,7 +1007,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -1028,7 +1028,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1057,7 +1056,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -1137,7 +1135,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1166,7 +1164,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1195,7 +1193,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1224,7 +1222,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1253,7 +1251,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1282,7 +1280,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1311,7 +1309,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1340,7 +1338,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1369,7 +1367,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1398,7 +1396,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1427,7 +1425,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1456,7 +1454,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1485,7 +1483,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1514,7 +1512,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1543,7 +1541,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1572,7 +1570,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1601,7 +1599,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1630,7 +1628,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1659,7 +1657,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1688,7 +1686,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1717,7 +1715,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1746,7 +1744,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1775,7 +1773,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1804,7 +1802,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1833,7 +1831,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1862,7 +1860,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1891,7 +1889,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1920,7 +1918,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1949,7 +1947,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1978,7 +1976,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -2007,7 +2005,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -2036,7 +2034,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -2065,7 +2063,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -2094,7 +2092,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2123,7 +2121,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2152,7 +2150,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2181,7 +2179,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2210,7 +2208,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2239,7 +2237,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2268,7 +2266,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2297,7 +2295,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2326,7 +2324,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2355,7 +2353,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2384,7 +2382,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2413,7 +2411,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2442,7 +2440,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2471,7 +2469,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2500,7 +2498,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2529,7 +2527,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2558,7 +2556,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2587,7 +2585,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2616,7 +2614,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2645,7 +2643,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2674,7 +2672,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2703,7 +2701,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2732,7 +2730,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2761,7 +2759,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2790,7 +2788,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2819,7 +2817,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2848,7 +2846,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2877,7 +2875,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2906,7 +2904,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2935,7 +2933,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2964,7 +2962,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2993,7 +2991,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -3022,7 +3020,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -3051,7 +3049,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -3080,7 +3078,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -3144,7 +3142,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B2" t="n">
@@ -3155,7 +3153,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B3" t="n">
@@ -3166,7 +3164,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B4" t="n">
@@ -3177,7 +3175,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B5" t="n">
@@ -3188,7 +3186,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B6" t="n">
@@ -3199,7 +3197,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B7" t="n">
@@ -3210,7 +3208,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B8" t="n">
@@ -3221,7 +3219,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B9" t="n">
@@ -3232,7 +3230,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B10" t="n">
@@ -3243,7 +3241,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B11" t="n">
@@ -3254,7 +3252,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B12" t="n">
@@ -3265,7 +3263,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B13" t="n">
@@ -3276,7 +3274,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B14" t="n">
@@ -3287,7 +3285,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B15" t="n">
@@ -3298,7 +3296,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B16" t="n">
@@ -3309,7 +3307,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B17" t="n">
@@ -3320,7 +3318,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B18" t="n">
@@ -3331,7 +3329,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B19" t="n">
@@ -3342,7 +3340,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B20" t="n">
@@ -3353,7 +3351,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B21" t="n">
@@ -3364,7 +3362,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B22" t="n">
@@ -3375,7 +3373,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B23" t="n">
@@ -3386,7 +3384,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B24" t="n">
@@ -3397,7 +3395,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B25" t="n">
@@ -3408,7 +3406,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B26" t="n">
@@ -3419,7 +3417,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B27" t="n">
@@ -3430,7 +3428,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B28" t="n">
@@ -3441,7 +3439,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B29" t="n">
@@ -3452,7 +3450,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B30" t="n">
@@ -3463,7 +3461,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B31" t="n">
@@ -3474,7 +3472,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B32" t="n">
@@ -3485,7 +3483,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B33" t="n">
@@ -3496,7 +3494,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B34" t="n">
@@ -3507,7 +3505,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B35" t="n">
@@ -3518,7 +3516,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B36" t="n">
@@ -3529,7 +3527,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B37" t="n">
@@ -3540,7 +3538,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B38" t="n">
@@ -3551,7 +3549,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B39" t="n">
@@ -3562,7 +3560,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B40" t="n">
@@ -3573,7 +3571,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B41" t="n">
@@ -3584,7 +3582,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B42" t="n">
@@ -3595,7 +3593,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B43" t="n">
@@ -3606,7 +3604,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B44" t="n">
@@ -3617,7 +3615,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B45" t="n">
@@ -3628,7 +3626,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B46" t="n">
@@ -3639,7 +3637,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B47" t="n">
@@ -3650,7 +3648,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B48" t="n">
@@ -3661,7 +3659,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B49" t="n">
@@ -3672,7 +3670,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B50" t="n">
@@ -3683,7 +3681,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B51" t="n">
@@ -3694,7 +3692,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B52" t="n">
@@ -3705,7 +3703,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B53" t="n">
@@ -3716,7 +3714,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B54" t="n">
@@ -3727,7 +3725,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B55" t="n">
@@ -3738,7 +3736,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B56" t="n">
@@ -3749,7 +3747,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B57" t="n">
@@ -3760,7 +3758,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B58" t="n">
@@ -3771,7 +3769,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B59" t="n">
@@ -3782,7 +3780,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B60" t="n">
@@ -3793,7 +3791,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B61" t="n">
@@ -3804,7 +3802,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B62" t="n">
@@ -3815,7 +3813,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B63" t="n">
@@ -3826,7 +3824,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B64" t="n">
@@ -3837,7 +3835,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B65" t="n">
@@ -3848,7 +3846,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B66" t="n">
@@ -3859,7 +3857,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B67" t="n">
@@ -3870,7 +3868,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B68" t="n">

--- a/output/Data and Chart Outputs/switzerland_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/switzerland_power_capacity_monthly.xlsx
@@ -12,8 +12,9 @@
     <sheet name="Chart - Net additions" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Monthly" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Check_ENTSOE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Snapshots" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Releases" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Check_Ember" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Snapshots" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Releases" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,8 +25,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -65,13 +66,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -161,7 +161,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Switzerland installed capacity, month-end (BFE / Pronovo register, rebuilt) (to Aug/26)</a:t>
+              <a:t>Switzerland installed capacity, month-end (BFE / Pronovo register, rebuilt) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -191,12 +191,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$69</f>
+              <f>'Chart'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -219,12 +219,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$69</f>
+              <f>'Chart'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -247,12 +247,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$69</f>
+              <f>'Chart'!$D$2:$D$71</f>
             </numRef>
           </val>
         </ser>
@@ -275,12 +275,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$69</f>
+              <f>'Chart'!$E$2:$E$71</f>
             </numRef>
           </val>
         </ser>
@@ -303,12 +303,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$69</f>
+              <f>'Chart'!$F$2:$F$71</f>
             </numRef>
           </val>
         </ser>
@@ -331,12 +331,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$69</f>
+              <f>'Chart'!$G$2:$G$71</f>
             </numRef>
           </val>
         </ser>
@@ -359,12 +359,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$69</f>
+              <f>'Chart'!$H$2:$H$71</f>
             </numRef>
           </val>
         </ser>
@@ -387,12 +387,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$69</f>
+              <f>'Chart'!$I$2:$I$71</f>
             </numRef>
           </val>
         </ser>
@@ -493,7 +493,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Switzerland installed capacity net additions of solar and wind per month (to Aug/26)</a:t>
+              <a:t>Switzerland installed capacity net additions of solar and wind per month (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -523,12 +523,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Net additions'!$A$2:$A$68</f>
+              <f>'Chart - Net additions'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Net additions'!$B$2:$B$68</f>
+              <f>'Chart - Net additions'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -551,12 +551,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Net additions'!$A$2:$A$68</f>
+              <f>'Chart - Net additions'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Net additions'!$C$2:$C$68</f>
+              <f>'Chart - Net additions'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -1007,6 +1007,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -1028,6 +1029,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1056,6 +1058,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -1081,7 +1084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1135,7 +1138,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1145,7 +1148,7 @@
         <v>0.2938</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2682</v>
+        <v>6.2695</v>
       </c>
       <c r="E2" t="n">
         <v>5.5567</v>
@@ -1154,17 +1157,17 @@
         <v>0.0844</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9306</v>
+        <v>2.9348</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1996</v>
+        <v>0.1993</v>
       </c>
       <c r="I2" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1174,7 +1177,7 @@
         <v>0.2938</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2686</v>
+        <v>6.2699</v>
       </c>
       <c r="E3" t="n">
         <v>5.5567</v>
@@ -1183,17 +1186,17 @@
         <v>0.0844</v>
       </c>
       <c r="G3" t="n">
-        <v>2.952</v>
+        <v>2.9562</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1996</v>
+        <v>0.1994</v>
       </c>
       <c r="I3" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1203,7 +1206,7 @@
         <v>0.2938</v>
       </c>
       <c r="D4" t="n">
-        <v>6.2846</v>
+        <v>6.2858</v>
       </c>
       <c r="E4" t="n">
         <v>5.5567</v>
@@ -1212,17 +1215,17 @@
         <v>0.0844</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9886</v>
+        <v>2.9925</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1996</v>
+        <v>0.1994</v>
       </c>
       <c r="I4" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1232,7 +1235,7 @@
         <v>0.2938</v>
       </c>
       <c r="D5" t="n">
-        <v>6.2846</v>
+        <v>6.2858</v>
       </c>
       <c r="E5" t="n">
         <v>5.5567</v>
@@ -1241,17 +1244,17 @@
         <v>0.0844</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0438</v>
+        <v>3.0478</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2126</v>
+        <v>0.2123</v>
       </c>
       <c r="I5" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1261,7 +1264,7 @@
         <v>0.2938</v>
       </c>
       <c r="D6" t="n">
-        <v>6.285100000000001</v>
+        <v>6.2863</v>
       </c>
       <c r="E6" t="n">
         <v>5.5567</v>
@@ -1270,17 +1273,17 @@
         <v>0.0844</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0907</v>
+        <v>3.0947</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2126</v>
+        <v>0.2123</v>
       </c>
       <c r="I6" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1290,7 +1293,7 @@
         <v>0.2938</v>
       </c>
       <c r="D7" t="n">
-        <v>6.285100000000001</v>
+        <v>6.2863</v>
       </c>
       <c r="E7" t="n">
         <v>5.5567</v>
@@ -1299,17 +1302,17 @@
         <v>0.0844</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1379</v>
+        <v>3.1416</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2126</v>
+        <v>0.2124</v>
       </c>
       <c r="I7" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1319,7 +1322,7 @@
         <v>0.2938</v>
       </c>
       <c r="D8" t="n">
-        <v>6.2852</v>
+        <v>6.2864</v>
       </c>
       <c r="E8" t="n">
         <v>5.5567</v>
@@ -1328,17 +1331,17 @@
         <v>0.0844</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1861</v>
+        <v>3.1898</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2126</v>
+        <v>0.2124</v>
       </c>
       <c r="I8" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1348,7 +1351,7 @@
         <v>0.2938</v>
       </c>
       <c r="D9" t="n">
-        <v>6.287199999999999</v>
+        <v>6.288399999999999</v>
       </c>
       <c r="E9" t="n">
         <v>5.5567</v>
@@ -1357,17 +1360,17 @@
         <v>0.0844</v>
       </c>
       <c r="G9" t="n">
-        <v>3.236</v>
+        <v>3.2404</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2136</v>
+        <v>0.2133</v>
       </c>
       <c r="I9" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1377,7 +1380,7 @@
         <v>0.2938</v>
       </c>
       <c r="D10" t="n">
-        <v>6.287199999999999</v>
+        <v>6.2885</v>
       </c>
       <c r="E10" t="n">
         <v>5.5567</v>
@@ -1386,17 +1389,17 @@
         <v>0.0844</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2784</v>
+        <v>3.2828</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2136</v>
+        <v>0.2133</v>
       </c>
       <c r="I10" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1406,7 +1409,7 @@
         <v>0.2938</v>
       </c>
       <c r="D11" t="n">
-        <v>6.2873</v>
+        <v>6.2885</v>
       </c>
       <c r="E11" t="n">
         <v>5.5567</v>
@@ -1415,17 +1418,17 @@
         <v>0.0844</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3328</v>
+        <v>3.3372</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2136</v>
+        <v>0.2133</v>
       </c>
       <c r="I11" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1435,7 +1438,7 @@
         <v>0.2939</v>
       </c>
       <c r="D12" t="n">
-        <v>6.2873</v>
+        <v>6.2885</v>
       </c>
       <c r="E12" t="n">
         <v>5.5567</v>
@@ -1444,17 +1447,17 @@
         <v>0.0844</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3846</v>
+        <v>3.389</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2136</v>
+        <v>0.2133</v>
       </c>
       <c r="I12" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1464,7 +1467,7 @@
         <v>0.2939</v>
       </c>
       <c r="D13" t="n">
-        <v>6.2873</v>
+        <v>6.2885</v>
       </c>
       <c r="E13" t="n">
         <v>5.5567</v>
@@ -1473,17 +1476,17 @@
         <v>0.0844</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4449</v>
+        <v>3.4493</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2136</v>
+        <v>0.2134</v>
       </c>
       <c r="I13" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1493,7 +1496,7 @@
         <v>0.2939</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2876</v>
+        <v>6.2889</v>
       </c>
       <c r="E14" t="n">
         <v>5.5567</v>
@@ -1502,17 +1505,17 @@
         <v>0.0844</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5007</v>
+        <v>3.5054</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2143</v>
+        <v>0.214</v>
       </c>
       <c r="I14" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1522,7 +1525,7 @@
         <v>0.2939</v>
       </c>
       <c r="D15" t="n">
-        <v>6.2882</v>
+        <v>6.2894</v>
       </c>
       <c r="E15" t="n">
         <v>5.5567</v>
@@ -1531,17 +1534,17 @@
         <v>0.0844</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5339</v>
+        <v>3.5386</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2145</v>
+        <v>0.2143</v>
       </c>
       <c r="I15" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1551,7 +1554,7 @@
         <v>0.2939</v>
       </c>
       <c r="D16" t="n">
-        <v>6.2885</v>
+        <v>6.2897</v>
       </c>
       <c r="E16" t="n">
         <v>5.5567</v>
@@ -1560,17 +1563,17 @@
         <v>0.0844</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5808</v>
+        <v>3.5855</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2145</v>
+        <v>0.2143</v>
       </c>
       <c r="I16" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1580,7 +1583,7 @@
         <v>0.2939</v>
       </c>
       <c r="D17" t="n">
-        <v>6.289</v>
+        <v>6.2903</v>
       </c>
       <c r="E17" t="n">
         <v>5.5567</v>
@@ -1589,17 +1592,17 @@
         <v>0.0844</v>
       </c>
       <c r="G17" t="n">
-        <v>3.6662</v>
+        <v>3.671</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2145</v>
+        <v>0.2143</v>
       </c>
       <c r="I17" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1609,7 +1612,7 @@
         <v>0.2939</v>
       </c>
       <c r="D18" t="n">
-        <v>6.2894</v>
+        <v>6.2906</v>
       </c>
       <c r="E18" t="n">
         <v>5.5567</v>
@@ -1618,17 +1621,17 @@
         <v>0.0844</v>
       </c>
       <c r="G18" t="n">
-        <v>3.7158</v>
+        <v>3.7207</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2145</v>
+        <v>0.2143</v>
       </c>
       <c r="I18" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1638,7 +1641,7 @@
         <v>0.2939</v>
       </c>
       <c r="D19" t="n">
-        <v>6.2895</v>
+        <v>6.2907</v>
       </c>
       <c r="E19" t="n">
         <v>5.5567</v>
@@ -1647,17 +1650,17 @@
         <v>0.0844</v>
       </c>
       <c r="G19" t="n">
-        <v>3.774</v>
+        <v>3.7789</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2148</v>
+        <v>0.2145</v>
       </c>
       <c r="I19" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1667,7 +1670,7 @@
         <v>0.2939</v>
       </c>
       <c r="D20" t="n">
-        <v>6.2908</v>
+        <v>6.292</v>
       </c>
       <c r="E20" t="n">
         <v>5.5567</v>
@@ -1676,17 +1679,17 @@
         <v>0.0844</v>
       </c>
       <c r="G20" t="n">
-        <v>3.8411</v>
+        <v>3.8461</v>
       </c>
       <c r="H20" t="n">
-        <v>0.216</v>
+        <v>0.2157</v>
       </c>
       <c r="I20" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1696,7 +1699,7 @@
         <v>0.2939</v>
       </c>
       <c r="D21" t="n">
-        <v>6.2908</v>
+        <v>6.292</v>
       </c>
       <c r="E21" t="n">
         <v>6.5017</v>
@@ -1705,17 +1708,17 @@
         <v>0.0844</v>
       </c>
       <c r="G21" t="n">
-        <v>3.9025</v>
+        <v>3.9075</v>
       </c>
       <c r="H21" t="n">
-        <v>0.216</v>
+        <v>0.2158</v>
       </c>
       <c r="I21" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1725,7 +1728,7 @@
         <v>0.2939</v>
       </c>
       <c r="D22" t="n">
-        <v>6.2918</v>
+        <v>6.293</v>
       </c>
       <c r="E22" t="n">
         <v>6.5017</v>
@@ -1734,17 +1737,17 @@
         <v>0.0844</v>
       </c>
       <c r="G22" t="n">
-        <v>3.9612</v>
+        <v>3.9662</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2225</v>
+        <v>0.2222</v>
       </c>
       <c r="I22" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1754,7 +1757,7 @@
         <v>0.2941</v>
       </c>
       <c r="D23" t="n">
-        <v>6.2918</v>
+        <v>6.293</v>
       </c>
       <c r="E23" t="n">
         <v>6.5017</v>
@@ -1763,17 +1766,17 @@
         <v>0.0844</v>
       </c>
       <c r="G23" t="n">
-        <v>4.0409</v>
+        <v>4.046</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2226</v>
+        <v>0.2223</v>
       </c>
       <c r="I23" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1783,7 +1786,7 @@
         <v>0.2981</v>
       </c>
       <c r="D24" t="n">
-        <v>6.2918</v>
+        <v>6.293</v>
       </c>
       <c r="E24" t="n">
         <v>6.5017</v>
@@ -1792,17 +1795,17 @@
         <v>0.0844</v>
       </c>
       <c r="G24" t="n">
-        <v>4.1107</v>
+        <v>4.1158</v>
       </c>
       <c r="H24" t="n">
-        <v>0.223</v>
+        <v>0.2227</v>
       </c>
       <c r="I24" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1812,7 +1815,7 @@
         <v>0.2981</v>
       </c>
       <c r="D25" t="n">
-        <v>6.2919</v>
+        <v>6.293100000000001</v>
       </c>
       <c r="E25" t="n">
         <v>6.5017</v>
@@ -1821,17 +1824,17 @@
         <v>0.0844</v>
       </c>
       <c r="G25" t="n">
-        <v>4.192</v>
+        <v>4.197100000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.223</v>
+        <v>0.2227</v>
       </c>
       <c r="I25" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1841,7 +1844,7 @@
         <v>0.2981</v>
       </c>
       <c r="D26" t="n">
-        <v>6.2995</v>
+        <v>6.3007</v>
       </c>
       <c r="E26" t="n">
         <v>6.5017</v>
@@ -1850,17 +1853,17 @@
         <v>0.0844</v>
       </c>
       <c r="G26" t="n">
-        <v>4.2814</v>
+        <v>4.2865</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2299</v>
+        <v>0.2296</v>
       </c>
       <c r="I26" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1870,7 +1873,7 @@
         <v>0.2981</v>
       </c>
       <c r="D27" t="n">
-        <v>6.3</v>
+        <v>6.3013</v>
       </c>
       <c r="E27" t="n">
         <v>6.5017</v>
@@ -1879,17 +1882,17 @@
         <v>0.0844</v>
       </c>
       <c r="G27" t="n">
-        <v>4.333</v>
+        <v>4.338100000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.23</v>
+        <v>0.2298</v>
       </c>
       <c r="I27" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1899,7 +1902,7 @@
         <v>0.2981</v>
       </c>
       <c r="D28" t="n">
-        <v>6.3002</v>
+        <v>6.301399999999999</v>
       </c>
       <c r="E28" t="n">
         <v>6.5017</v>
@@ -1908,17 +1911,17 @@
         <v>0.0844</v>
       </c>
       <c r="G28" t="n">
-        <v>4.4213</v>
+        <v>4.426399999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2301</v>
+        <v>0.2299</v>
       </c>
       <c r="I28" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1928,7 +1931,7 @@
         <v>0.2981</v>
       </c>
       <c r="D29" t="n">
-        <v>6.3002</v>
+        <v>6.301399999999999</v>
       </c>
       <c r="E29" t="n">
         <v>6.5017</v>
@@ -1937,17 +1940,17 @@
         <v>0.0844</v>
       </c>
       <c r="G29" t="n">
-        <v>4.5442</v>
+        <v>4.549399999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0.236</v>
+        <v>0.2358</v>
       </c>
       <c r="I29" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1957,7 +1960,7 @@
         <v>0.2981</v>
       </c>
       <c r="D30" t="n">
-        <v>6.3002</v>
+        <v>6.301399999999999</v>
       </c>
       <c r="E30" t="n">
         <v>6.5017</v>
@@ -1966,17 +1969,17 @@
         <v>0.0844</v>
       </c>
       <c r="G30" t="n">
-        <v>4.6432</v>
+        <v>4.6485</v>
       </c>
       <c r="H30" t="n">
-        <v>0.236</v>
+        <v>0.2358</v>
       </c>
       <c r="I30" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1986,7 +1989,7 @@
         <v>0.2981</v>
       </c>
       <c r="D31" t="n">
-        <v>6.3002</v>
+        <v>6.301399999999999</v>
       </c>
       <c r="E31" t="n">
         <v>6.5017</v>
@@ -1995,17 +1998,17 @@
         <v>0.0844</v>
       </c>
       <c r="G31" t="n">
-        <v>4.7755</v>
+        <v>4.7809</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2361</v>
+        <v>0.2359</v>
       </c>
       <c r="I31" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -2015,7 +2018,7 @@
         <v>0.2981</v>
       </c>
       <c r="D32" t="n">
-        <v>6.310899999999999</v>
+        <v>6.3122</v>
       </c>
       <c r="E32" t="n">
         <v>6.5017</v>
@@ -2024,17 +2027,17 @@
         <v>0.0844</v>
       </c>
       <c r="G32" t="n">
-        <v>4.9304</v>
+        <v>4.9363</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2361</v>
+        <v>0.2359</v>
       </c>
       <c r="I32" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -2044,7 +2047,7 @@
         <v>0.2981</v>
       </c>
       <c r="D33" t="n">
-        <v>6.3125</v>
+        <v>6.313800000000001</v>
       </c>
       <c r="E33" t="n">
         <v>6.5017</v>
@@ -2053,17 +2056,17 @@
         <v>0.0844</v>
       </c>
       <c r="G33" t="n">
-        <v>5.079800000000001</v>
+        <v>5.0857</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2361</v>
+        <v>0.2359</v>
       </c>
       <c r="I33" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -2073,7 +2076,7 @@
         <v>0.2981</v>
       </c>
       <c r="D34" t="n">
-        <v>6.3125</v>
+        <v>6.313800000000001</v>
       </c>
       <c r="E34" t="n">
         <v>6.5017</v>
@@ -2082,17 +2085,17 @@
         <v>0.0844</v>
       </c>
       <c r="G34" t="n">
-        <v>5.212</v>
+        <v>5.217899999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2363</v>
+        <v>0.2361</v>
       </c>
       <c r="I34" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2102,7 +2105,7 @@
         <v>0.2981</v>
       </c>
       <c r="D35" t="n">
-        <v>6.3125</v>
+        <v>6.313800000000001</v>
       </c>
       <c r="E35" t="n">
         <v>6.5017</v>
@@ -2111,17 +2114,17 @@
         <v>0.0844</v>
       </c>
       <c r="G35" t="n">
-        <v>5.371</v>
+        <v>5.3771</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2363</v>
+        <v>0.2361</v>
       </c>
       <c r="I35" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2131,7 +2134,7 @@
         <v>0.2982</v>
       </c>
       <c r="D36" t="n">
-        <v>6.3143</v>
+        <v>6.315600000000001</v>
       </c>
       <c r="E36" t="n">
         <v>6.5017</v>
@@ -2140,17 +2143,17 @@
         <v>0.0844</v>
       </c>
       <c r="G36" t="n">
-        <v>5.521199999999999</v>
+        <v>5.5275</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2363</v>
+        <v>0.2361</v>
       </c>
       <c r="I36" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2160,7 +2163,7 @@
         <v>0.2982</v>
       </c>
       <c r="D37" t="n">
-        <v>6.3143</v>
+        <v>6.315600000000001</v>
       </c>
       <c r="E37" t="n">
         <v>6.5017</v>
@@ -2169,17 +2172,17 @@
         <v>0.0844</v>
       </c>
       <c r="G37" t="n">
-        <v>5.6713</v>
+        <v>5.677899999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2363</v>
+        <v>0.2361</v>
       </c>
       <c r="I37" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2189,7 +2192,7 @@
         <v>0.2982</v>
       </c>
       <c r="D38" t="n">
-        <v>6.3143</v>
+        <v>6.315600000000001</v>
       </c>
       <c r="E38" t="n">
         <v>6.5017</v>
@@ -2198,17 +2201,17 @@
         <v>0.0844</v>
       </c>
       <c r="G38" t="n">
-        <v>5.8262</v>
+        <v>5.8333</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2376</v>
+        <v>0.2374</v>
       </c>
       <c r="I38" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2218,7 +2221,7 @@
         <v>0.2982</v>
       </c>
       <c r="D39" t="n">
-        <v>6.352600000000001</v>
+        <v>6.353899999999999</v>
       </c>
       <c r="E39" t="n">
         <v>6.5017</v>
@@ -2227,17 +2230,17 @@
         <v>0.0985</v>
       </c>
       <c r="G39" t="n">
-        <v>5.9133</v>
+        <v>5.9204</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2376</v>
+        <v>0.2374</v>
       </c>
       <c r="I39" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2247,7 +2250,7 @@
         <v>0.2982</v>
       </c>
       <c r="D40" t="n">
-        <v>6.352600000000001</v>
+        <v>6.353899999999999</v>
       </c>
       <c r="E40" t="n">
         <v>6.5017</v>
@@ -2256,17 +2259,17 @@
         <v>0.0985</v>
       </c>
       <c r="G40" t="n">
-        <v>6.042</v>
+        <v>6.0492</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2377</v>
+        <v>0.2375</v>
       </c>
       <c r="I40" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2276,7 +2279,7 @@
         <v>0.2982</v>
       </c>
       <c r="D41" t="n">
-        <v>6.352600000000001</v>
+        <v>6.353899999999999</v>
       </c>
       <c r="E41" t="n">
         <v>6.5017</v>
@@ -2285,17 +2288,17 @@
         <v>0.0985</v>
       </c>
       <c r="G41" t="n">
-        <v>6.207199999999999</v>
+        <v>6.2147</v>
       </c>
       <c r="H41" t="n">
-        <v>0.238</v>
+        <v>0.2378</v>
       </c>
       <c r="I41" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2305,7 +2308,7 @@
         <v>0.2987</v>
       </c>
       <c r="D42" t="n">
-        <v>6.3549</v>
+        <v>6.356100000000001</v>
       </c>
       <c r="E42" t="n">
         <v>6.5017</v>
@@ -2314,17 +2317,17 @@
         <v>0.0985</v>
       </c>
       <c r="G42" t="n">
-        <v>6.3504</v>
+        <v>6.3584</v>
       </c>
       <c r="H42" t="n">
-        <v>0.238</v>
+        <v>0.2378</v>
       </c>
       <c r="I42" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2334,7 +2337,7 @@
         <v>0.2987</v>
       </c>
       <c r="D43" t="n">
-        <v>6.3549</v>
+        <v>6.356100000000001</v>
       </c>
       <c r="E43" t="n">
         <v>6.5017</v>
@@ -2343,17 +2346,17 @@
         <v>0.0985</v>
       </c>
       <c r="G43" t="n">
-        <v>6.5022</v>
+        <v>6.5102</v>
       </c>
       <c r="H43" t="n">
-        <v>0.238</v>
+        <v>0.2378</v>
       </c>
       <c r="I43" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2363,7 +2366,7 @@
         <v>0.2987</v>
       </c>
       <c r="D44" t="n">
-        <v>6.3549</v>
+        <v>6.356100000000001</v>
       </c>
       <c r="E44" t="n">
         <v>6.5017</v>
@@ -2372,17 +2375,17 @@
         <v>0.0985</v>
       </c>
       <c r="G44" t="n">
-        <v>6.6579</v>
+        <v>6.666</v>
       </c>
       <c r="H44" t="n">
-        <v>0.238</v>
+        <v>0.2378</v>
       </c>
       <c r="I44" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2392,7 +2395,7 @@
         <v>0.2987</v>
       </c>
       <c r="D45" t="n">
-        <v>6.3611</v>
+        <v>6.3623</v>
       </c>
       <c r="E45" t="n">
         <v>6.5017</v>
@@ -2401,17 +2404,17 @@
         <v>0.0985</v>
       </c>
       <c r="G45" t="n">
-        <v>6.8123</v>
+        <v>6.8205</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2382</v>
+        <v>0.238</v>
       </c>
       <c r="I45" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2421,7 +2424,7 @@
         <v>0.2987</v>
       </c>
       <c r="D46" t="n">
-        <v>6.3611</v>
+        <v>6.3623</v>
       </c>
       <c r="E46" t="n">
         <v>6.5017</v>
@@ -2430,17 +2433,17 @@
         <v>0.0985</v>
       </c>
       <c r="G46" t="n">
-        <v>6.9313</v>
+        <v>6.9398</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2382</v>
+        <v>0.238</v>
       </c>
       <c r="I46" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2450,7 +2453,7 @@
         <v>0.2987</v>
       </c>
       <c r="D47" t="n">
-        <v>6.3611</v>
+        <v>6.3623</v>
       </c>
       <c r="E47" t="n">
         <v>6.5017</v>
@@ -2459,17 +2462,17 @@
         <v>0.0985</v>
       </c>
       <c r="G47" t="n">
-        <v>7.0623</v>
+        <v>7.0715</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2382</v>
+        <v>0.238</v>
       </c>
       <c r="I47" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2479,7 +2482,7 @@
         <v>0.2987</v>
       </c>
       <c r="D48" t="n">
-        <v>6.3611</v>
+        <v>6.3623</v>
       </c>
       <c r="E48" t="n">
         <v>6.5017</v>
@@ -2488,17 +2491,17 @@
         <v>0.0985</v>
       </c>
       <c r="G48" t="n">
-        <v>7.2127</v>
+        <v>7.2222</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2384</v>
+        <v>0.2382</v>
       </c>
       <c r="I48" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2508,7 +2511,7 @@
         <v>0.2987</v>
       </c>
       <c r="D49" t="n">
-        <v>6.3612</v>
+        <v>6.3624</v>
       </c>
       <c r="E49" t="n">
         <v>6.5017</v>
@@ -2517,17 +2520,17 @@
         <v>0.0985</v>
       </c>
       <c r="G49" t="n">
-        <v>7.360300000000001</v>
+        <v>7.369800000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2384</v>
+        <v>0.2382</v>
       </c>
       <c r="I49" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2537,7 +2540,7 @@
         <v>0.2987</v>
       </c>
       <c r="D50" t="n">
-        <v>6.3612</v>
+        <v>6.3624</v>
       </c>
       <c r="E50" t="n">
         <v>6.5017</v>
@@ -2546,17 +2549,17 @@
         <v>0.0985</v>
       </c>
       <c r="G50" t="n">
-        <v>7.4929</v>
+        <v>7.5032</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2387</v>
+        <v>0.2385</v>
       </c>
       <c r="I50" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2566,7 +2569,7 @@
         <v>0.2987</v>
       </c>
       <c r="D51" t="n">
-        <v>6.3612</v>
+        <v>6.3624</v>
       </c>
       <c r="E51" t="n">
         <v>6.5017</v>
@@ -2575,17 +2578,17 @@
         <v>0.0985</v>
       </c>
       <c r="G51" t="n">
-        <v>7.5634</v>
+        <v>7.574199999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2391</v>
+        <v>0.2389</v>
       </c>
       <c r="I51" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2595,7 +2598,7 @@
         <v>0.2987</v>
       </c>
       <c r="D52" t="n">
-        <v>6.3612</v>
+        <v>6.3624</v>
       </c>
       <c r="E52" t="n">
         <v>6.5017</v>
@@ -2604,17 +2607,17 @@
         <v>0.0985</v>
       </c>
       <c r="G52" t="n">
-        <v>7.6643</v>
+        <v>7.6754</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2391</v>
+        <v>0.2389</v>
       </c>
       <c r="I52" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2624,7 +2627,7 @@
         <v>0.2987</v>
       </c>
       <c r="D53" t="n">
-        <v>6.3615</v>
+        <v>6.3628</v>
       </c>
       <c r="E53" t="n">
         <v>6.5017</v>
@@ -2633,17 +2636,17 @@
         <v>0.0985</v>
       </c>
       <c r="G53" t="n">
-        <v>7.809600000000001</v>
+        <v>7.8212</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2392</v>
+        <v>0.239</v>
       </c>
       <c r="I53" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2653,7 +2656,7 @@
         <v>0.2987</v>
       </c>
       <c r="D54" t="n">
-        <v>6.3615</v>
+        <v>6.3628</v>
       </c>
       <c r="E54" t="n">
         <v>6.5017</v>
@@ -2662,17 +2665,17 @@
         <v>0.0985</v>
       </c>
       <c r="G54" t="n">
-        <v>7.8996</v>
+        <v>7.9114</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2394</v>
+        <v>0.2392</v>
       </c>
       <c r="I54" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2682,7 +2685,7 @@
         <v>0.2987</v>
       </c>
       <c r="D55" t="n">
-        <v>6.3615</v>
+        <v>6.3628</v>
       </c>
       <c r="E55" t="n">
         <v>6.5017</v>
@@ -2691,17 +2694,17 @@
         <v>0.0985</v>
       </c>
       <c r="G55" t="n">
-        <v>7.9901</v>
+        <v>8.002699999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2396</v>
+        <v>0.2394</v>
       </c>
       <c r="I55" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2711,7 +2714,7 @@
         <v>0.2987</v>
       </c>
       <c r="D56" t="n">
-        <v>6.3615</v>
+        <v>6.3628</v>
       </c>
       <c r="E56" t="n">
         <v>6.5017</v>
@@ -2720,17 +2723,17 @@
         <v>0.0985</v>
       </c>
       <c r="G56" t="n">
-        <v>8.077399999999999</v>
+        <v>8.0909</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2412</v>
+        <v>0.241</v>
       </c>
       <c r="I56" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2740,7 +2743,7 @@
         <v>0.2987</v>
       </c>
       <c r="D57" t="n">
-        <v>6.3615</v>
+        <v>6.3628</v>
       </c>
       <c r="E57" t="n">
         <v>6.5017</v>
@@ -2749,7 +2752,7 @@
         <v>0.0985</v>
       </c>
       <c r="G57" t="n">
-        <v>8.179500000000001</v>
+        <v>8.194000000000001</v>
       </c>
       <c r="H57" t="n">
         <v>0.2412</v>
@@ -2759,7 +2762,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2769,7 +2772,7 @@
         <v>0.2987</v>
       </c>
       <c r="D58" t="n">
-        <v>6.3615</v>
+        <v>6.3628</v>
       </c>
       <c r="E58" t="n">
         <v>6.5017</v>
@@ -2778,7 +2781,7 @@
         <v>0.0985</v>
       </c>
       <c r="G58" t="n">
-        <v>8.2568</v>
+        <v>8.2728</v>
       </c>
       <c r="H58" t="n">
         <v>0.242</v>
@@ -2788,7 +2791,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2798,7 +2801,7 @@
         <v>0.2987</v>
       </c>
       <c r="D59" t="n">
-        <v>6.3729</v>
+        <v>6.3742</v>
       </c>
       <c r="E59" t="n">
         <v>6.5017</v>
@@ -2807,7 +2810,7 @@
         <v>0.0985</v>
       </c>
       <c r="G59" t="n">
-        <v>8.3498</v>
+        <v>8.3674</v>
       </c>
       <c r="H59" t="n">
         <v>0.2423</v>
@@ -2817,7 +2820,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2827,7 +2830,7 @@
         <v>0.2987</v>
       </c>
       <c r="D60" t="n">
-        <v>6.3741</v>
+        <v>6.3754</v>
       </c>
       <c r="E60" t="n">
         <v>6.5017</v>
@@ -2836,7 +2839,7 @@
         <v>0.1077</v>
       </c>
       <c r="G60" t="n">
-        <v>8.44</v>
+        <v>8.4602</v>
       </c>
       <c r="H60" t="n">
         <v>0.2424</v>
@@ -2846,7 +2849,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2856,7 +2859,7 @@
         <v>0.2987</v>
       </c>
       <c r="D61" t="n">
-        <v>6.3741</v>
+        <v>6.3754</v>
       </c>
       <c r="E61" t="n">
         <v>6.5017</v>
@@ -2865,17 +2868,17 @@
         <v>0.1097</v>
       </c>
       <c r="G61" t="n">
-        <v>8.528700000000001</v>
+        <v>8.550700000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2425</v>
+        <v>0.2424</v>
       </c>
       <c r="I61" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2885,7 +2888,7 @@
         <v>0.2987</v>
       </c>
       <c r="D62" t="n">
-        <v>6.3741</v>
+        <v>6.3754</v>
       </c>
       <c r="E62" t="n">
         <v>6.5017</v>
@@ -2894,17 +2897,17 @@
         <v>0.1097</v>
       </c>
       <c r="G62" t="n">
-        <v>8.606</v>
+        <v>8.6311</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2439</v>
+        <v>0.2438</v>
       </c>
       <c r="I62" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2914,7 +2917,7 @@
         <v>0.2987</v>
       </c>
       <c r="D63" t="n">
-        <v>6.3741</v>
+        <v>6.3754</v>
       </c>
       <c r="E63" t="n">
         <v>6.5017</v>
@@ -2923,7 +2926,7 @@
         <v>0.1097</v>
       </c>
       <c r="G63" t="n">
-        <v>8.6471</v>
+        <v>8.674100000000001</v>
       </c>
       <c r="H63" t="n">
         <v>0.2439</v>
@@ -2933,7 +2936,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2943,7 +2946,7 @@
         <v>0.2987</v>
       </c>
       <c r="D64" t="n">
-        <v>6.3741</v>
+        <v>6.3754</v>
       </c>
       <c r="E64" t="n">
         <v>6.5017</v>
@@ -2952,7 +2955,7 @@
         <v>0.1097</v>
       </c>
       <c r="G64" t="n">
-        <v>8.688000000000001</v>
+        <v>8.719299999999999</v>
       </c>
       <c r="H64" t="n">
         <v>0.2439</v>
@@ -2962,7 +2965,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2972,7 +2975,7 @@
         <v>0.2987</v>
       </c>
       <c r="D65" t="n">
-        <v>6.3741</v>
+        <v>6.3754</v>
       </c>
       <c r="E65" t="n">
         <v>6.5017</v>
@@ -2981,17 +2984,17 @@
         <v>0.1097</v>
       </c>
       <c r="G65" t="n">
-        <v>8.7501</v>
+        <v>8.7897</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2442</v>
+        <v>0.2441</v>
       </c>
       <c r="I65" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -3001,7 +3004,7 @@
         <v>0.2987</v>
       </c>
       <c r="D66" t="n">
-        <v>6.3741</v>
+        <v>6.3754</v>
       </c>
       <c r="E66" t="n">
         <v>6.5017</v>
@@ -3010,7 +3013,7 @@
         <v>0.1097</v>
       </c>
       <c r="G66" t="n">
-        <v>8.787799999999999</v>
+        <v>8.837299999999999</v>
       </c>
       <c r="H66" t="n">
         <v>0.2446</v>
@@ -3020,7 +3023,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -3030,7 +3033,7 @@
         <v>0.2987</v>
       </c>
       <c r="D67" t="n">
-        <v>6.3741</v>
+        <v>6.3754</v>
       </c>
       <c r="E67" t="n">
         <v>6.5017</v>
@@ -3039,17 +3042,17 @@
         <v>0.1097</v>
       </c>
       <c r="G67" t="n">
-        <v>8.8085</v>
+        <v>8.8659</v>
       </c>
       <c r="H67" t="n">
-        <v>0.2448</v>
+        <v>0.2447</v>
       </c>
       <c r="I67" t="n">
         <v>0.3538</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -3059,7 +3062,7 @@
         <v>0.2987</v>
       </c>
       <c r="D68" t="n">
-        <v>6.3741</v>
+        <v>6.3754</v>
       </c>
       <c r="E68" t="n">
         <v>6.5017</v>
@@ -3068,7 +3071,7 @@
         <v>0.1097</v>
       </c>
       <c r="G68" t="n">
-        <v>8.8247</v>
+        <v>8.897600000000001</v>
       </c>
       <c r="H68" t="n">
         <v>0.2449</v>
@@ -3078,7 +3081,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -3088,7 +3091,7 @@
         <v>0.2987</v>
       </c>
       <c r="D69" t="n">
-        <v>6.3741</v>
+        <v>6.3754</v>
       </c>
       <c r="E69" t="n">
         <v>6.5017</v>
@@ -3097,12 +3100,70 @@
         <v>0.1097</v>
       </c>
       <c r="G69" t="n">
-        <v>8.8292</v>
+        <v>8.9091</v>
       </c>
       <c r="H69" t="n">
-        <v>0.2449</v>
+        <v>0.245</v>
       </c>
       <c r="I69" t="n">
+        <v>0.3538</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>3.0146</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6.3754</v>
+      </c>
+      <c r="E70" t="n">
+        <v>6.5017</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="G70" t="n">
+        <v>8.910600000000001</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.3538</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B71" t="n">
+        <v>3.0146</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="D71" t="n">
+        <v>6.3754</v>
+      </c>
+      <c r="E71" t="n">
+        <v>6.5017</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="G71" t="n">
+        <v>8.911200000000001</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="I71" t="n">
         <v>0.3538</v>
       </c>
     </row>
@@ -3118,7 +3179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3142,40 +3203,40 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B2" t="n">
-        <v>21.40000000000009</v>
+        <v>21.39999999999964</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B3" t="n">
-        <v>36.59999999999991</v>
+        <v>36.30000000000018</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B4" t="n">
-        <v>55.20000000000027</v>
+        <v>55.30000000000018</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B5" t="n">
@@ -3186,40 +3247,40 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B6" t="n">
-        <v>47.20000000000027</v>
+        <v>46.90000000000009</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B7" t="n">
-        <v>48.19999999999982</v>
+        <v>48.20000000000027</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B8" t="n">
-        <v>49.90000000000009</v>
+        <v>50.59999999999991</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B9" t="n">
@@ -3230,29 +3291,29 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B10" t="n">
-        <v>54.40000000000009</v>
+        <v>54.39999999999964</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B11" t="n">
-        <v>51.79999999999973</v>
+        <v>51.80000000000018</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B12" t="n">
@@ -3263,29 +3324,29 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B13" t="n">
-        <v>55.79999999999973</v>
+        <v>56.09999999999991</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B14" t="n">
-        <v>33.20000000000027</v>
+        <v>33.19999999999982</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B15" t="n">
@@ -3296,51 +3357,51 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B16" t="n">
-        <v>85.39999999999964</v>
+        <v>85.5</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B17" t="n">
-        <v>49.60000000000036</v>
+        <v>49.69999999999982</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B18" t="n">
-        <v>58.19999999999982</v>
+        <v>58.20000000000027</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B19" t="n">
-        <v>67.09999999999991</v>
+        <v>67.19999999999982</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B20" t="n">
@@ -3351,7 +3412,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B21" t="n">
@@ -3362,29 +3423,29 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B22" t="n">
-        <v>79.70000000000027</v>
+        <v>79.80000000000018</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B23" t="n">
-        <v>69.79999999999973</v>
+        <v>69.80000000000018</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B24" t="n">
@@ -3395,7 +3456,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B25" t="n">
@@ -3406,7 +3467,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B26" t="n">
@@ -3417,73 +3478,73 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B27" t="n">
-        <v>88.30000000000018</v>
+        <v>88.29999999999927</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B28" t="n">
-        <v>122.8999999999996</v>
+        <v>123</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B29" t="n">
-        <v>99</v>
+        <v>99.10000000000036</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B30" t="n">
-        <v>132.3000000000002</v>
+        <v>132.3999999999996</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B31" t="n">
-        <v>154.8999999999996</v>
+        <v>155.4000000000005</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B32" t="n">
-        <v>149.4000000000005</v>
+        <v>149.3999999999996</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B33" t="n">
@@ -3494,95 +3555,95 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B34" t="n">
-        <v>159</v>
+        <v>159.2000000000007</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B35" t="n">
-        <v>150.1999999999998</v>
+        <v>150.3999999999996</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B36" t="n">
-        <v>150.1000000000004</v>
+        <v>150.3999999999996</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B37" t="n">
-        <v>154.8999999999996</v>
+        <v>155.4000000000005</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B38" t="n">
-        <v>87.10000000000036</v>
+        <v>87.09999999999945</v>
       </c>
       <c r="C38" t="n">
         <v>14.09999999999999</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B39" t="n">
-        <v>128.6999999999998</v>
+        <v>128.8000000000002</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B40" t="n">
-        <v>165.1999999999998</v>
+        <v>165.5</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B41" t="n">
-        <v>143.1999999999998</v>
+        <v>143.6999999999998</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B42" t="n">
@@ -3593,62 +3654,62 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B43" t="n">
-        <v>155.6999999999998</v>
+        <v>155.8000000000002</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B44" t="n">
-        <v>154.4000000000005</v>
+        <v>154.5</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B45" t="n">
-        <v>119</v>
+        <v>119.3000000000002</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B46" t="n">
-        <v>131</v>
+        <v>131.6999999999998</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B47" t="n">
-        <v>150.3999999999996</v>
+        <v>150.6999999999998</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B48" t="n">
@@ -3659,222 +3720,244 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B49" t="n">
-        <v>132.5999999999995</v>
+        <v>133.3999999999996</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B50" t="n">
-        <v>70.5</v>
+        <v>71</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B51" t="n">
-        <v>100.9000000000005</v>
+        <v>101.1999999999998</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B52" t="n">
-        <v>145.3000000000002</v>
+        <v>145.8000000000002</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B53" t="n">
-        <v>90</v>
+        <v>90.19999999999982</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B54" t="n">
-        <v>90.5</v>
+        <v>91.30000000000018</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B55" t="n">
-        <v>87.29999999999927</v>
+        <v>88.19999999999982</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B56" t="n">
-        <v>102.1000000000004</v>
+        <v>103.1000000000004</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B57" t="n">
-        <v>77.29999999999927</v>
+        <v>78.79999999999927</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B58" t="n">
-        <v>93</v>
+        <v>94.60000000000036</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B59" t="n">
-        <v>90.20000000000073</v>
+        <v>92.80000000000109</v>
       </c>
       <c r="C59" t="n">
         <v>9.200000000000003</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B60" t="n">
-        <v>88.70000000000073</v>
+        <v>90.5</v>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B61" t="n">
-        <v>77.29999999999927</v>
+        <v>80.39999999999964</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B62" t="n">
-        <v>41.10000000000036</v>
+        <v>43</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B63" t="n">
-        <v>40.89999999999964</v>
+        <v>45.19999999999891</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B64" t="n">
-        <v>62.10000000000036</v>
+        <v>70.40000000000146</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B65" t="n">
-        <v>37.69999999999891</v>
+        <v>47.59999999999854</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B66" t="n">
-        <v>20.70000000000073</v>
+        <v>28.60000000000036</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B67" t="n">
-        <v>16.20000000000073</v>
+        <v>31.70000000000073</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B68" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="C68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B70" t="n">
+        <v>0.6000000000003638</v>
+      </c>
+      <c r="C70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3890,7 +3973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:P71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3980,7 +4063,7 @@
         <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>6268.2</v>
+        <v>6269.5</v>
       </c>
       <c r="C2" t="n">
         <v>293.8</v>
@@ -3989,7 +4072,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2930.6</v>
+        <v>2934.8</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -4001,22 +4084,22 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>199.6</v>
+        <v>199.3</v>
       </c>
       <c r="J2" t="n">
         <v>353.8</v>
       </c>
       <c r="K2" t="n">
-        <v>13145.1</v>
+        <v>13150.2</v>
       </c>
       <c r="L2" t="n">
         <v>5556.7</v>
       </c>
       <c r="N2" t="n">
-        <v>2533.80639</v>
+        <v>2535.4922</v>
       </c>
       <c r="O2" t="n">
-        <v>11824.90154</v>
+        <v>11826.16004</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -4027,7 +4110,7 @@
         <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>6268.6</v>
+        <v>6269.9</v>
       </c>
       <c r="C3" t="n">
         <v>293.8</v>
@@ -4036,7 +4119,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>2952</v>
+        <v>2956.2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -4048,22 +4131,22 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>199.6</v>
+        <v>199.4</v>
       </c>
       <c r="J3" t="n">
         <v>353.8</v>
       </c>
       <c r="K3" t="n">
-        <v>13166.8</v>
+        <v>13172.1</v>
       </c>
       <c r="L3" t="n">
         <v>5556.7</v>
       </c>
       <c r="N3" t="n">
-        <v>2552.1422</v>
+        <v>2553.82801</v>
       </c>
       <c r="O3" t="n">
-        <v>11825.28554</v>
+        <v>11826.54404</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -4074,7 +4157,7 @@
         <v>44256</v>
       </c>
       <c r="B4" t="n">
-        <v>6284.6</v>
+        <v>6285.8</v>
       </c>
       <c r="C4" t="n">
         <v>293.8</v>
@@ -4083,7 +4166,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>2988.6</v>
+        <v>2992.5</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -4095,22 +4178,22 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>199.6</v>
+        <v>199.4</v>
       </c>
       <c r="J4" t="n">
         <v>353.8</v>
       </c>
       <c r="K4" t="n">
-        <v>13219.4</v>
+        <v>13224.3</v>
       </c>
       <c r="L4" t="n">
         <v>5556.7</v>
       </c>
       <c r="N4" t="n">
-        <v>2585.94227</v>
+        <v>2587.31832</v>
       </c>
       <c r="O4" t="n">
-        <v>11841.23554</v>
+        <v>11842.49404</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -4121,7 +4204,7 @@
         <v>44287</v>
       </c>
       <c r="B5" t="n">
-        <v>6284.6</v>
+        <v>6285.8</v>
       </c>
       <c r="C5" t="n">
         <v>293.8</v>
@@ -4130,7 +4213,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>3043.8</v>
+        <v>3047.8</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -4142,22 +4225,22 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>212.6</v>
+        <v>212.3</v>
       </c>
       <c r="J5" t="n">
         <v>353.8</v>
       </c>
       <c r="K5" t="n">
-        <v>13287.5</v>
+        <v>13292.5</v>
       </c>
       <c r="L5" t="n">
         <v>5556.7</v>
       </c>
       <c r="N5" t="n">
-        <v>2637.64459</v>
+        <v>2639.02064</v>
       </c>
       <c r="O5" t="n">
-        <v>11841.23554</v>
+        <v>11842.49404</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -4168,7 +4251,7 @@
         <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>6285.1</v>
+        <v>6286.3</v>
       </c>
       <c r="C6" t="n">
         <v>293.8</v>
@@ -4177,7 +4260,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3090.7</v>
+        <v>3094.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -4189,22 +4272,22 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>212.6</v>
+        <v>212.3</v>
       </c>
       <c r="J6" t="n">
         <v>353.8</v>
       </c>
       <c r="K6" t="n">
-        <v>13334.9</v>
+        <v>13339.9</v>
       </c>
       <c r="L6" t="n">
         <v>5556.7</v>
       </c>
       <c r="N6" t="n">
-        <v>2681.04486</v>
+        <v>2682.42091</v>
       </c>
       <c r="O6" t="n">
-        <v>11841.73554</v>
+        <v>11842.99404</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -4215,7 +4298,7 @@
         <v>44348</v>
       </c>
       <c r="B7" t="n">
-        <v>6285.1</v>
+        <v>6286.3</v>
       </c>
       <c r="C7" t="n">
         <v>293.8</v>
@@ -4224,7 +4307,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>3137.9</v>
+        <v>3141.6</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -4236,22 +4319,22 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>212.6</v>
+        <v>212.4</v>
       </c>
       <c r="J7" t="n">
         <v>353.8</v>
       </c>
       <c r="K7" t="n">
-        <v>13382.2</v>
+        <v>13387</v>
       </c>
       <c r="L7" t="n">
         <v>5556.7</v>
       </c>
       <c r="N7" t="n">
-        <v>2721.55314</v>
+        <v>2722.65968</v>
       </c>
       <c r="O7" t="n">
-        <v>11841.73554</v>
+        <v>11842.99404</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
@@ -4262,7 +4345,7 @@
         <v>44378</v>
       </c>
       <c r="B8" t="n">
-        <v>6285.2</v>
+        <v>6286.4</v>
       </c>
       <c r="C8" t="n">
         <v>293.8</v>
@@ -4271,7 +4354,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>3186.1</v>
+        <v>3189.8</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -4283,22 +4366,22 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>212.6</v>
+        <v>212.4</v>
       </c>
       <c r="J8" t="n">
         <v>353.8</v>
       </c>
       <c r="K8" t="n">
-        <v>13430.5</v>
+        <v>13435.2</v>
       </c>
       <c r="L8" t="n">
         <v>5556.7</v>
       </c>
       <c r="N8" t="n">
-        <v>2767.44305</v>
+        <v>2768.54959</v>
       </c>
       <c r="O8" t="n">
-        <v>11841.85604</v>
+        <v>11843.11454</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -4309,7 +4392,7 @@
         <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>6287.2</v>
+        <v>6288.4</v>
       </c>
       <c r="C9" t="n">
         <v>293.8</v>
@@ -4318,7 +4401,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>3236</v>
+        <v>3240.4</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -4330,22 +4413,22 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>213.6</v>
+        <v>213.3</v>
       </c>
       <c r="J9" t="n">
         <v>353.8</v>
       </c>
       <c r="K9" t="n">
-        <v>13483.3</v>
+        <v>13488.8</v>
       </c>
       <c r="L9" t="n">
         <v>5556.7</v>
       </c>
       <c r="N9" t="n">
-        <v>2811.07923</v>
+        <v>2812.87427</v>
       </c>
       <c r="O9" t="n">
-        <v>11843.85604</v>
+        <v>11845.11454</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -4356,7 +4439,7 @@
         <v>44440</v>
       </c>
       <c r="B10" t="n">
-        <v>6287.2</v>
+        <v>6288.5</v>
       </c>
       <c r="C10" t="n">
         <v>293.8</v>
@@ -4365,7 +4448,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>3278.4</v>
+        <v>3282.8</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -4377,22 +4460,22 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>213.6</v>
+        <v>213.3</v>
       </c>
       <c r="J10" t="n">
         <v>353.8</v>
       </c>
       <c r="K10" t="n">
-        <v>13525.7</v>
+        <v>13531.2</v>
       </c>
       <c r="L10" t="n">
         <v>5556.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2850.88481</v>
+        <v>2852.67985</v>
       </c>
       <c r="O10" t="n">
-        <v>11843.87454</v>
+        <v>11845.13304</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
@@ -4403,7 +4486,7 @@
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>6287.3</v>
+        <v>6288.5</v>
       </c>
       <c r="C11" t="n">
         <v>293.8</v>
@@ -4412,7 +4495,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3332.8</v>
+        <v>3337.2</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -4424,22 +4507,22 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>213.6</v>
+        <v>213.3</v>
       </c>
       <c r="J11" t="n">
         <v>353.8</v>
       </c>
       <c r="K11" t="n">
-        <v>13580.2</v>
+        <v>13585.7</v>
       </c>
       <c r="L11" t="n">
         <v>5556.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2901.37304</v>
+        <v>2903.16808</v>
       </c>
       <c r="O11" t="n">
-        <v>11843.96454</v>
+        <v>11845.22304</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
@@ -4450,7 +4533,7 @@
         <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>6287.3</v>
+        <v>6288.5</v>
       </c>
       <c r="C12" t="n">
         <v>293.9</v>
@@ -4459,7 +4542,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3384.6</v>
+        <v>3389</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -4471,22 +4554,22 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>213.6</v>
+        <v>213.3</v>
       </c>
       <c r="J12" t="n">
         <v>353.8</v>
       </c>
       <c r="K12" t="n">
-        <v>13632.1</v>
+        <v>13637.5</v>
       </c>
       <c r="L12" t="n">
         <v>5556.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2950.20555</v>
+        <v>2951.98083</v>
       </c>
       <c r="O12" t="n">
-        <v>11843.96454</v>
+        <v>11845.22304</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
@@ -4497,7 +4580,7 @@
         <v>44531</v>
       </c>
       <c r="B13" t="n">
-        <v>6287.3</v>
+        <v>6288.5</v>
       </c>
       <c r="C13" t="n">
         <v>293.9</v>
@@ -4506,7 +4589,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>3444.9</v>
+        <v>3449.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -4518,22 +4601,22 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>213.6</v>
+        <v>213.4</v>
       </c>
       <c r="J13" t="n">
         <v>353.8</v>
       </c>
       <c r="K13" t="n">
-        <v>13692.5</v>
+        <v>13697.9</v>
       </c>
       <c r="L13" t="n">
         <v>5556.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3004.71785</v>
+        <v>3006.51263</v>
       </c>
       <c r="O13" t="n">
-        <v>11843.96454</v>
+        <v>11845.22304</v>
       </c>
       <c r="P13" t="b">
         <v>0</v>
@@ -4544,7 +4627,7 @@
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>6287.6</v>
+        <v>6288.9</v>
       </c>
       <c r="C14" t="n">
         <v>293.9</v>
@@ -4553,7 +4636,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>3500.7</v>
+        <v>3505.4</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -4565,22 +4648,22 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>214.3</v>
+        <v>214</v>
       </c>
       <c r="J14" t="n">
         <v>353.8</v>
       </c>
       <c r="K14" t="n">
-        <v>13749.3</v>
+        <v>13754.9</v>
       </c>
       <c r="L14" t="n">
         <v>5556.7</v>
       </c>
       <c r="N14" t="n">
-        <v>3054.41296</v>
+        <v>3056.38561</v>
       </c>
       <c r="O14" t="n">
-        <v>11844.30454</v>
+        <v>11845.56304</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
@@ -4591,7 +4674,7 @@
         <v>44593</v>
       </c>
       <c r="B15" t="n">
-        <v>6288.2</v>
+        <v>6289.4</v>
       </c>
       <c r="C15" t="n">
         <v>293.9</v>
@@ -4600,7 +4683,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>3533.9</v>
+        <v>3538.6</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -4612,22 +4695,22 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>214.5</v>
+        <v>214.3</v>
       </c>
       <c r="J15" t="n">
         <v>353.8</v>
       </c>
       <c r="K15" t="n">
-        <v>13783.2</v>
+        <v>13788.9</v>
       </c>
       <c r="L15" t="n">
         <v>5556.7</v>
       </c>
       <c r="N15" t="n">
-        <v>3084.83164</v>
+        <v>3086.81895</v>
       </c>
       <c r="O15" t="n">
-        <v>11844.82854</v>
+        <v>11846.08704</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
@@ -4638,7 +4721,7 @@
         <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>6288.5</v>
+        <v>6289.7</v>
       </c>
       <c r="C16" t="n">
         <v>293.9</v>
@@ -4647,7 +4730,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>3580.8</v>
+        <v>3585.5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -4659,22 +4742,22 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>214.5</v>
+        <v>214.3</v>
       </c>
       <c r="J16" t="n">
         <v>353.8</v>
       </c>
       <c r="K16" t="n">
-        <v>13830.5</v>
+        <v>13836.2</v>
       </c>
       <c r="L16" t="n">
         <v>5556.7</v>
       </c>
       <c r="N16" t="n">
-        <v>3128.67397</v>
+        <v>3130.66128</v>
       </c>
       <c r="O16" t="n">
-        <v>11845.12854</v>
+        <v>11846.38704</v>
       </c>
       <c r="P16" t="b">
         <v>0</v>
@@ -4685,7 +4768,7 @@
         <v>44652</v>
       </c>
       <c r="B17" t="n">
-        <v>6289</v>
+        <v>6290.3</v>
       </c>
       <c r="C17" t="n">
         <v>293.9</v>
@@ -4694,7 +4777,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>3666.2</v>
+        <v>3671</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -4706,22 +4789,22 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>214.5</v>
+        <v>214.3</v>
       </c>
       <c r="J17" t="n">
         <v>353.8</v>
       </c>
       <c r="K17" t="n">
-        <v>13916.4</v>
+        <v>13922.2</v>
       </c>
       <c r="L17" t="n">
         <v>5556.7</v>
       </c>
       <c r="N17" t="n">
-        <v>3203.86524</v>
+        <v>3205.88077</v>
       </c>
       <c r="O17" t="n">
-        <v>11845.72354</v>
+        <v>11846.98204</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
@@ -4732,7 +4815,7 @@
         <v>44682</v>
       </c>
       <c r="B18" t="n">
-        <v>6289.4</v>
+        <v>6290.6</v>
       </c>
       <c r="C18" t="n">
         <v>293.9</v>
@@ -4741,7 +4824,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>3715.8</v>
+        <v>3720.7</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -4753,22 +4836,22 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>214.5</v>
+        <v>214.3</v>
       </c>
       <c r="J18" t="n">
         <v>353.8</v>
       </c>
       <c r="K18" t="n">
-        <v>13966.4</v>
+        <v>13972.3</v>
       </c>
       <c r="L18" t="n">
         <v>5556.7</v>
       </c>
       <c r="N18" t="n">
-        <v>3250.02661</v>
+        <v>3252.061940000001</v>
       </c>
       <c r="O18" t="n">
-        <v>11846.04554</v>
+        <v>11847.30404</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -4779,7 +4862,7 @@
         <v>44713</v>
       </c>
       <c r="B19" t="n">
-        <v>6289.5</v>
+        <v>6290.7</v>
       </c>
       <c r="C19" t="n">
         <v>293.9</v>
@@ -4788,7 +4871,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>3774</v>
+        <v>3778.9</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -4800,22 +4883,22 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>214.8</v>
+        <v>214.5</v>
       </c>
       <c r="J19" t="n">
         <v>353.8</v>
       </c>
       <c r="K19" t="n">
-        <v>14024.9</v>
+        <v>14030.9</v>
       </c>
       <c r="L19" t="n">
         <v>5556.7</v>
       </c>
       <c r="N19" t="n">
-        <v>3305.8426</v>
+        <v>3307.87793</v>
       </c>
       <c r="O19" t="n">
-        <v>11846.15754</v>
+        <v>11847.41604</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
@@ -4826,7 +4909,7 @@
         <v>44743</v>
       </c>
       <c r="B20" t="n">
-        <v>6290.8</v>
+        <v>6292</v>
       </c>
       <c r="C20" t="n">
         <v>293.9</v>
@@ -4835,7 +4918,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>3841.1</v>
+        <v>3846.1</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -4847,22 +4930,22 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>216</v>
+        <v>215.7</v>
       </c>
       <c r="J20" t="n">
         <v>353.8</v>
       </c>
       <c r="K20" t="n">
-        <v>14094.6</v>
+        <v>14100.5</v>
       </c>
       <c r="L20" t="n">
         <v>5556.7</v>
       </c>
       <c r="N20" t="n">
-        <v>3366.78858</v>
+        <v>3368.82391</v>
       </c>
       <c r="O20" t="n">
-        <v>11847.46254</v>
+        <v>11848.72104</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
@@ -4873,7 +4956,7 @@
         <v>44774</v>
       </c>
       <c r="B21" t="n">
-        <v>6290.8</v>
+        <v>6292</v>
       </c>
       <c r="C21" t="n">
         <v>293.9</v>
@@ -4882,7 +4965,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>3902.5</v>
+        <v>3907.5</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -4894,22 +4977,22 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>216</v>
+        <v>215.8</v>
       </c>
       <c r="J21" t="n">
         <v>353.8</v>
       </c>
       <c r="K21" t="n">
-        <v>14156</v>
+        <v>14162</v>
       </c>
       <c r="L21" t="n">
         <v>6501.7</v>
       </c>
       <c r="N21" t="n">
-        <v>3425.93877</v>
+        <v>3427.99998</v>
       </c>
       <c r="O21" t="n">
-        <v>12792.46254</v>
+        <v>12793.72104</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
@@ -4920,7 +5003,7 @@
         <v>44805</v>
       </c>
       <c r="B22" t="n">
-        <v>6291.8</v>
+        <v>6293</v>
       </c>
       <c r="C22" t="n">
         <v>293.9</v>
@@ -4929,7 +5012,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>3961.2</v>
+        <v>3966.2</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -4941,22 +5024,22 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>222.5</v>
+        <v>222.2</v>
       </c>
       <c r="J22" t="n">
         <v>353.8</v>
       </c>
       <c r="K22" t="n">
-        <v>14222.2</v>
+        <v>14228.2</v>
       </c>
       <c r="L22" t="n">
         <v>6501.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3480.95277</v>
+        <v>3483.03632</v>
       </c>
       <c r="O22" t="n">
-        <v>12793.45254</v>
+        <v>12794.71104</v>
       </c>
       <c r="P22" t="b">
         <v>0</v>
@@ -4967,7 +5050,7 @@
         <v>44835</v>
       </c>
       <c r="B23" t="n">
-        <v>6291.8</v>
+        <v>6293</v>
       </c>
       <c r="C23" t="n">
         <v>294.1</v>
@@ -4976,7 +5059,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>4040.9</v>
+        <v>4046</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -4988,22 +5071,22 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>222.6</v>
+        <v>222.3</v>
       </c>
       <c r="J23" t="n">
         <v>353.8</v>
       </c>
       <c r="K23" t="n">
-        <v>14302.1</v>
+        <v>14308.2</v>
       </c>
       <c r="L23" t="n">
         <v>6501.7</v>
       </c>
       <c r="N23" t="n">
-        <v>3557.3303</v>
+        <v>3559.413849999999</v>
       </c>
       <c r="O23" t="n">
-        <v>12793.45254</v>
+        <v>12794.71104</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
@@ -5014,7 +5097,7 @@
         <v>44866</v>
       </c>
       <c r="B24" t="n">
-        <v>6291.8</v>
+        <v>6293</v>
       </c>
       <c r="C24" t="n">
         <v>298.1</v>
@@ -5023,7 +5106,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>4110.7</v>
+        <v>4115.8</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -5035,22 +5118,22 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>223</v>
+        <v>222.7</v>
       </c>
       <c r="J24" t="n">
         <v>353.8</v>
       </c>
       <c r="K24" t="n">
-        <v>14376.4</v>
+        <v>14382.5</v>
       </c>
       <c r="L24" t="n">
         <v>6501.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3623.59853</v>
+        <v>3625.68616</v>
       </c>
       <c r="O24" t="n">
-        <v>12793.45254</v>
+        <v>12794.71104</v>
       </c>
       <c r="P24" t="b">
         <v>0</v>
@@ -5061,7 +5144,7 @@
         <v>44896</v>
       </c>
       <c r="B25" t="n">
-        <v>6291.9</v>
+        <v>6293.1</v>
       </c>
       <c r="C25" t="n">
         <v>298.1</v>
@@ -5070,7 +5153,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>4192</v>
+        <v>4197.1</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -5082,22 +5165,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>223</v>
+        <v>222.7</v>
       </c>
       <c r="J25" t="n">
         <v>353.8</v>
       </c>
       <c r="K25" t="n">
-        <v>14457.7</v>
+        <v>14463.8</v>
       </c>
       <c r="L25" t="n">
         <v>6501.7</v>
       </c>
       <c r="N25" t="n">
-        <v>3702.2743</v>
+        <v>3704.36193</v>
       </c>
       <c r="O25" t="n">
-        <v>12793.54354</v>
+        <v>12794.80204</v>
       </c>
       <c r="P25" t="b">
         <v>0</v>
@@ -5108,7 +5191,7 @@
         <v>44927</v>
       </c>
       <c r="B26" t="n">
-        <v>6299.5</v>
+        <v>6300.7</v>
       </c>
       <c r="C26" t="n">
         <v>298.1</v>
@@ -5117,7 +5200,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>4281.4</v>
+        <v>4286.5</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -5129,22 +5212,22 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>229.9</v>
+        <v>229.6</v>
       </c>
       <c r="J26" t="n">
         <v>353.8</v>
       </c>
       <c r="K26" t="n">
-        <v>14561.6</v>
+        <v>14567.7</v>
       </c>
       <c r="L26" t="n">
         <v>6501.7</v>
       </c>
       <c r="N26" t="n">
-        <v>3787.60544</v>
+        <v>3789.69763</v>
       </c>
       <c r="O26" t="n">
-        <v>12801.14154</v>
+        <v>12802.40004</v>
       </c>
       <c r="P26" t="b">
         <v>0</v>
@@ -5155,7 +5238,7 @@
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>6300</v>
+        <v>6301.3</v>
       </c>
       <c r="C27" t="n">
         <v>298.1</v>
@@ -5164,7 +5247,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>4333</v>
+        <v>4338.1</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -5176,22 +5259,22 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>230</v>
+        <v>229.8</v>
       </c>
       <c r="J27" t="n">
         <v>353.8</v>
       </c>
       <c r="K27" t="n">
-        <v>14613.9</v>
+        <v>14620</v>
       </c>
       <c r="L27" t="n">
         <v>6501.7</v>
       </c>
       <c r="N27" t="n">
-        <v>3836.71795</v>
+        <v>3838.81014</v>
       </c>
       <c r="O27" t="n">
-        <v>12801.68654</v>
+        <v>12802.94504</v>
       </c>
       <c r="P27" t="b">
         <v>0</v>
@@ -5202,7 +5285,7 @@
         <v>44986</v>
       </c>
       <c r="B28" t="n">
-        <v>6300.2</v>
+        <v>6301.4</v>
       </c>
       <c r="C28" t="n">
         <v>298.1</v>
@@ -5211,7 +5294,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>4421.3</v>
+        <v>4426.4</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -5223,22 +5306,22 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>230.1</v>
+        <v>229.9</v>
       </c>
       <c r="J28" t="n">
         <v>353.8</v>
       </c>
       <c r="K28" t="n">
-        <v>14702.5</v>
+        <v>14708.6</v>
       </c>
       <c r="L28" t="n">
         <v>6501.7</v>
       </c>
       <c r="N28" t="n">
-        <v>3922.0642</v>
+        <v>3924.15639</v>
       </c>
       <c r="O28" t="n">
-        <v>12801.83954</v>
+        <v>12803.09804</v>
       </c>
       <c r="P28" t="b">
         <v>0</v>
@@ -5249,7 +5332,7 @@
         <v>45017</v>
       </c>
       <c r="B29" t="n">
-        <v>6300.2</v>
+        <v>6301.4</v>
       </c>
       <c r="C29" t="n">
         <v>298.1</v>
@@ -5258,7 +5341,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>4544.2</v>
+        <v>4549.4</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -5270,22 +5353,22 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>236</v>
+        <v>235.8</v>
       </c>
       <c r="J29" t="n">
         <v>353.8</v>
       </c>
       <c r="K29" t="n">
-        <v>14831.3</v>
+        <v>14837.5</v>
       </c>
       <c r="L29" t="n">
         <v>6501.7</v>
       </c>
       <c r="N29" t="n">
-        <v>4039.81627</v>
+        <v>4042.00926</v>
       </c>
       <c r="O29" t="n">
-        <v>12801.83954</v>
+        <v>12803.09804</v>
       </c>
       <c r="P29" t="b">
         <v>0</v>
@@ -5296,7 +5379,7 @@
         <v>45047</v>
       </c>
       <c r="B30" t="n">
-        <v>6300.2</v>
+        <v>6301.4</v>
       </c>
       <c r="C30" t="n">
         <v>298.1</v>
@@ -5305,7 +5388,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>4643.2</v>
+        <v>4648.5</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -5317,22 +5400,22 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>236</v>
+        <v>235.8</v>
       </c>
       <c r="J30" t="n">
         <v>353.8</v>
       </c>
       <c r="K30" t="n">
-        <v>14930.3</v>
+        <v>14936.6</v>
       </c>
       <c r="L30" t="n">
         <v>6501.7</v>
       </c>
       <c r="N30" t="n">
-        <v>4136.26149</v>
+        <v>4138.50171</v>
       </c>
       <c r="O30" t="n">
-        <v>12801.83954</v>
+        <v>12803.09804</v>
       </c>
       <c r="P30" t="b">
         <v>0</v>
@@ -5343,7 +5426,7 @@
         <v>45078</v>
       </c>
       <c r="B31" t="n">
-        <v>6300.2</v>
+        <v>6301.4</v>
       </c>
       <c r="C31" t="n">
         <v>298.1</v>
@@ -5352,7 +5435,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>4775.5</v>
+        <v>4780.9</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -5364,22 +5447,22 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>236.1</v>
+        <v>235.9</v>
       </c>
       <c r="J31" t="n">
         <v>353.8</v>
       </c>
       <c r="K31" t="n">
-        <v>15062.6</v>
+        <v>15069.1</v>
       </c>
       <c r="L31" t="n">
         <v>6501.7</v>
       </c>
       <c r="N31" t="n">
-        <v>4264.472640000001</v>
+        <v>4266.726539999999</v>
       </c>
       <c r="O31" t="n">
-        <v>12801.83954</v>
+        <v>12803.09804</v>
       </c>
       <c r="P31" t="b">
         <v>0</v>
@@ -5390,7 +5473,7 @@
         <v>45108</v>
       </c>
       <c r="B32" t="n">
-        <v>6310.9</v>
+        <v>6312.2</v>
       </c>
       <c r="C32" t="n">
         <v>298.1</v>
@@ -5399,7 +5482,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>4930.4</v>
+        <v>4936.3</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -5411,22 +5494,22 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>236.1</v>
+        <v>235.9</v>
       </c>
       <c r="J32" t="n">
         <v>353.8</v>
       </c>
       <c r="K32" t="n">
-        <v>15228.2</v>
+        <v>15235.2</v>
       </c>
       <c r="L32" t="n">
         <v>6501.7</v>
       </c>
       <c r="N32" t="n">
-        <v>4414.776150000001</v>
+        <v>4417.39671</v>
       </c>
       <c r="O32" t="n">
-        <v>12812.59104</v>
+        <v>12813.84954</v>
       </c>
       <c r="P32" t="b">
         <v>0</v>
@@ -5437,7 +5520,7 @@
         <v>45139</v>
       </c>
       <c r="B33" t="n">
-        <v>6312.5</v>
+        <v>6313.8</v>
       </c>
       <c r="C33" t="n">
         <v>298.1</v>
@@ -5446,7 +5529,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>5079.8</v>
+        <v>5085.7</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -5458,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>236.1</v>
+        <v>235.9</v>
       </c>
       <c r="J33" t="n">
         <v>353.8</v>
       </c>
       <c r="K33" t="n">
-        <v>15379.2</v>
+        <v>15386.2</v>
       </c>
       <c r="L33" t="n">
         <v>6501.7</v>
       </c>
       <c r="N33" t="n">
-        <v>4560.777609999999</v>
+        <v>4563.41157</v>
       </c>
       <c r="O33" t="n">
-        <v>12814.19104</v>
+        <v>12815.44954</v>
       </c>
       <c r="P33" t="b">
         <v>0</v>
@@ -5484,7 +5567,7 @@
         <v>45170</v>
       </c>
       <c r="B34" t="n">
-        <v>6312.5</v>
+        <v>6313.8</v>
       </c>
       <c r="C34" t="n">
         <v>298.1</v>
@@ -5493,7 +5576,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>5212</v>
+        <v>5217.9</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -5505,22 +5588,22 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>236.3</v>
+        <v>236.1</v>
       </c>
       <c r="J34" t="n">
         <v>353.8</v>
       </c>
       <c r="K34" t="n">
-        <v>15511.7</v>
+        <v>15518.7</v>
       </c>
       <c r="L34" t="n">
         <v>6501.7</v>
       </c>
       <c r="N34" t="n">
-        <v>4688.76133</v>
+        <v>4691.422769999999</v>
       </c>
       <c r="O34" t="n">
-        <v>12814.19104</v>
+        <v>12815.44954</v>
       </c>
       <c r="P34" t="b">
         <v>0</v>
@@ -5531,7 +5614,7 @@
         <v>45200</v>
       </c>
       <c r="B35" t="n">
-        <v>6312.5</v>
+        <v>6313.8</v>
       </c>
       <c r="C35" t="n">
         <v>298.1</v>
@@ -5540,7 +5623,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>5371</v>
+        <v>5377.1</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -5552,22 +5635,22 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>236.3</v>
+        <v>236.1</v>
       </c>
       <c r="J35" t="n">
         <v>353.8</v>
       </c>
       <c r="K35" t="n">
-        <v>15670.7</v>
+        <v>15677.8</v>
       </c>
       <c r="L35" t="n">
         <v>6501.7</v>
       </c>
       <c r="N35" t="n">
-        <v>4844.320390000001</v>
+        <v>4847.00515</v>
       </c>
       <c r="O35" t="n">
-        <v>12814.19104</v>
+        <v>12815.44954</v>
       </c>
       <c r="P35" t="b">
         <v>0</v>
@@ -5578,7 +5661,7 @@
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>6314.3</v>
+        <v>6315.6</v>
       </c>
       <c r="C36" t="n">
         <v>298.2</v>
@@ -5587,7 +5670,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>5521.2</v>
+        <v>5527.5</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -5599,22 +5682,22 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>236.3</v>
+        <v>236.1</v>
       </c>
       <c r="J36" t="n">
         <v>353.8</v>
       </c>
       <c r="K36" t="n">
-        <v>15822.8</v>
+        <v>15830.2</v>
       </c>
       <c r="L36" t="n">
         <v>6501.7</v>
       </c>
       <c r="N36" t="n">
-        <v>4991.81148</v>
+        <v>4994.58466</v>
       </c>
       <c r="O36" t="n">
-        <v>12816.01004</v>
+        <v>12817.26854</v>
       </c>
       <c r="P36" t="b">
         <v>0</v>
@@ -5625,7 +5708,7 @@
         <v>45261</v>
       </c>
       <c r="B37" t="n">
-        <v>6314.3</v>
+        <v>6315.6</v>
       </c>
       <c r="C37" t="n">
         <v>298.2</v>
@@ -5634,7 +5717,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>5671.3</v>
+        <v>5677.9</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -5646,22 +5729,22 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>236.3</v>
+        <v>236.1</v>
       </c>
       <c r="J37" t="n">
         <v>353.8</v>
       </c>
       <c r="K37" t="n">
-        <v>15972.9</v>
+        <v>15980.6</v>
       </c>
       <c r="L37" t="n">
         <v>6501.7</v>
       </c>
       <c r="N37" t="n">
-        <v>5140.493109999999</v>
+        <v>5143.47213</v>
       </c>
       <c r="O37" t="n">
-        <v>12816.02354</v>
+        <v>12817.28204</v>
       </c>
       <c r="P37" t="b">
         <v>0</v>
@@ -5672,7 +5755,7 @@
         <v>45292</v>
       </c>
       <c r="B38" t="n">
-        <v>6314.3</v>
+        <v>6315.6</v>
       </c>
       <c r="C38" t="n">
         <v>298.2</v>
@@ -5681,7 +5764,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>5826.2</v>
+        <v>5833.3</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -5693,22 +5776,22 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>237.6</v>
+        <v>237.4</v>
       </c>
       <c r="J38" t="n">
         <v>353.8</v>
       </c>
       <c r="K38" t="n">
-        <v>16129.2</v>
+        <v>16137.3</v>
       </c>
       <c r="L38" t="n">
         <v>6501.7</v>
       </c>
       <c r="N38" t="n">
-        <v>5292.030049999999</v>
+        <v>5295.03183</v>
       </c>
       <c r="O38" t="n">
-        <v>12816.02354</v>
+        <v>12817.28204</v>
       </c>
       <c r="P38" t="b">
         <v>0</v>
@@ -5719,7 +5802,7 @@
         <v>45323</v>
       </c>
       <c r="B39" t="n">
-        <v>6352.6</v>
+        <v>6353.9</v>
       </c>
       <c r="C39" t="n">
         <v>298.2</v>
@@ -5728,7 +5811,7 @@
         <v>98.5</v>
       </c>
       <c r="E39" t="n">
-        <v>5913.3</v>
+        <v>5920.4</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -5740,22 +5823,22 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>237.6</v>
+        <v>237.4</v>
       </c>
       <c r="J39" t="n">
         <v>353.8</v>
       </c>
       <c r="K39" t="n">
-        <v>16268.7</v>
+        <v>16276.8</v>
       </c>
       <c r="L39" t="n">
         <v>6501.7</v>
       </c>
       <c r="N39" t="n">
-        <v>5376.752949999999</v>
+        <v>5379.77365</v>
       </c>
       <c r="O39" t="n">
-        <v>12854.27354</v>
+        <v>12855.53204</v>
       </c>
       <c r="P39" t="b">
         <v>0</v>
@@ -5766,7 +5849,7 @@
         <v>45352</v>
       </c>
       <c r="B40" t="n">
-        <v>6352.6</v>
+        <v>6353.9</v>
       </c>
       <c r="C40" t="n">
         <v>298.2</v>
@@ -5775,7 +5858,7 @@
         <v>98.5</v>
       </c>
       <c r="E40" t="n">
-        <v>6042</v>
+        <v>6049.2</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -5787,22 +5870,22 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>237.7</v>
+        <v>237.5</v>
       </c>
       <c r="J40" t="n">
         <v>353.8</v>
       </c>
       <c r="K40" t="n">
-        <v>16397.4</v>
+        <v>16405.7</v>
       </c>
       <c r="L40" t="n">
         <v>6501.7</v>
       </c>
       <c r="N40" t="n">
-        <v>5501.29702</v>
+        <v>5504.35338</v>
       </c>
       <c r="O40" t="n">
-        <v>12854.28854</v>
+        <v>12855.54704</v>
       </c>
       <c r="P40" t="b">
         <v>0</v>
@@ -5813,7 +5896,7 @@
         <v>45383</v>
       </c>
       <c r="B41" t="n">
-        <v>6352.6</v>
+        <v>6353.9</v>
       </c>
       <c r="C41" t="n">
         <v>298.2</v>
@@ -5822,7 +5905,7 @@
         <v>98.5</v>
       </c>
       <c r="E41" t="n">
-        <v>6207.2</v>
+        <v>6214.7</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -5834,22 +5917,22 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>238</v>
+        <v>237.8</v>
       </c>
       <c r="J41" t="n">
         <v>353.8</v>
       </c>
       <c r="K41" t="n">
-        <v>16562.9</v>
+        <v>16571.4</v>
       </c>
       <c r="L41" t="n">
         <v>6501.7</v>
       </c>
       <c r="N41" t="n">
-        <v>5662.815519999999</v>
+        <v>5665.873329999999</v>
       </c>
       <c r="O41" t="n">
-        <v>12854.28854</v>
+        <v>12855.54704</v>
       </c>
       <c r="P41" t="b">
         <v>0</v>
@@ -5860,7 +5943,7 @@
         <v>45413</v>
       </c>
       <c r="B42" t="n">
-        <v>6354.9</v>
+        <v>6356.1</v>
       </c>
       <c r="C42" t="n">
         <v>298.7</v>
@@ -5869,7 +5952,7 @@
         <v>98.5</v>
       </c>
       <c r="E42" t="n">
-        <v>6350.4</v>
+        <v>6358.4</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -5881,22 +5964,22 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>238</v>
+        <v>237.8</v>
       </c>
       <c r="J42" t="n">
         <v>353.8</v>
       </c>
       <c r="K42" t="n">
-        <v>16708.8</v>
+        <v>16717.9</v>
       </c>
       <c r="L42" t="n">
         <v>6501.7</v>
       </c>
       <c r="N42" t="n">
-        <v>5803.769</v>
+        <v>5807.33116</v>
       </c>
       <c r="O42" t="n">
-        <v>12856.55694</v>
+        <v>12857.81544</v>
       </c>
       <c r="P42" t="b">
         <v>0</v>
@@ -5907,7 +5990,7 @@
         <v>45444</v>
       </c>
       <c r="B43" t="n">
-        <v>6354.9</v>
+        <v>6356.1</v>
       </c>
       <c r="C43" t="n">
         <v>298.7</v>
@@ -5916,7 +5999,7 @@
         <v>98.5</v>
       </c>
       <c r="E43" t="n">
-        <v>6502.2</v>
+        <v>6510.2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -5928,22 +6011,22 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>238</v>
+        <v>237.8</v>
       </c>
       <c r="J43" t="n">
         <v>353.8</v>
       </c>
       <c r="K43" t="n">
-        <v>16860.7</v>
+        <v>16869.8</v>
       </c>
       <c r="L43" t="n">
         <v>6501.7</v>
       </c>
       <c r="N43" t="n">
-        <v>5954.06866</v>
+        <v>5957.645199999999</v>
       </c>
       <c r="O43" t="n">
-        <v>12856.55694</v>
+        <v>12857.81544</v>
       </c>
       <c r="P43" t="b">
         <v>0</v>
@@ -5954,7 +6037,7 @@
         <v>45474</v>
       </c>
       <c r="B44" t="n">
-        <v>6354.9</v>
+        <v>6356.1</v>
       </c>
       <c r="C44" t="n">
         <v>298.7</v>
@@ -5963,7 +6046,7 @@
         <v>98.5</v>
       </c>
       <c r="E44" t="n">
-        <v>6657.9</v>
+        <v>6666</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -5975,22 +6058,22 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>238</v>
+        <v>237.8</v>
       </c>
       <c r="J44" t="n">
         <v>353.8</v>
       </c>
       <c r="K44" t="n">
-        <v>17016.5</v>
+        <v>17025.6</v>
       </c>
       <c r="L44" t="n">
         <v>6501.7</v>
       </c>
       <c r="N44" t="n">
-        <v>6103.68816</v>
+        <v>6107.310439999999</v>
       </c>
       <c r="O44" t="n">
-        <v>12856.55694</v>
+        <v>12857.81544</v>
       </c>
       <c r="P44" t="b">
         <v>0</v>
@@ -6001,7 +6084,7 @@
         <v>45505</v>
       </c>
       <c r="B45" t="n">
-        <v>6361.1</v>
+        <v>6362.3</v>
       </c>
       <c r="C45" t="n">
         <v>298.7</v>
@@ -6010,7 +6093,7 @@
         <v>98.5</v>
       </c>
       <c r="E45" t="n">
-        <v>6812.3</v>
+        <v>6820.5</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -6022,22 +6105,22 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>238.2</v>
+        <v>238</v>
       </c>
       <c r="J45" t="n">
         <v>353.8</v>
       </c>
       <c r="K45" t="n">
-        <v>17177.2</v>
+        <v>17186.4</v>
       </c>
       <c r="L45" t="n">
         <v>6501.7</v>
       </c>
       <c r="N45" t="n">
-        <v>6256.345490000001</v>
+        <v>6260.05686</v>
       </c>
       <c r="O45" t="n">
-        <v>12862.75694</v>
+        <v>12864.01544</v>
       </c>
       <c r="P45" t="b">
         <v>0</v>
@@ -6048,7 +6131,7 @@
         <v>45536</v>
       </c>
       <c r="B46" t="n">
-        <v>6361.1</v>
+        <v>6362.3</v>
       </c>
       <c r="C46" t="n">
         <v>298.7</v>
@@ -6057,7 +6140,7 @@
         <v>98.5</v>
       </c>
       <c r="E46" t="n">
-        <v>6931.3</v>
+        <v>6939.8</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -6069,22 +6152,22 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>238.2</v>
+        <v>238</v>
       </c>
       <c r="J46" t="n">
         <v>353.8</v>
       </c>
       <c r="K46" t="n">
-        <v>17296.2</v>
+        <v>17305.7</v>
       </c>
       <c r="L46" t="n">
         <v>6501.7</v>
       </c>
       <c r="N46" t="n">
-        <v>6373.50627</v>
+        <v>6377.5145</v>
       </c>
       <c r="O46" t="n">
-        <v>12862.75694</v>
+        <v>12864.01544</v>
       </c>
       <c r="P46" t="b">
         <v>0</v>
@@ -6095,7 +6178,7 @@
         <v>45566</v>
       </c>
       <c r="B47" t="n">
-        <v>6361.1</v>
+        <v>6362.3</v>
       </c>
       <c r="C47" t="n">
         <v>298.7</v>
@@ -6104,7 +6187,7 @@
         <v>98.5</v>
       </c>
       <c r="E47" t="n">
-        <v>7062.3</v>
+        <v>7071.5</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -6116,22 +6199,22 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>238.2</v>
+        <v>238</v>
       </c>
       <c r="J47" t="n">
         <v>353.8</v>
       </c>
       <c r="K47" t="n">
-        <v>17427.2</v>
+        <v>17437.5</v>
       </c>
       <c r="L47" t="n">
         <v>6501.7</v>
       </c>
       <c r="N47" t="n">
-        <v>6501.681489999999</v>
+        <v>6505.987599999999</v>
       </c>
       <c r="O47" t="n">
-        <v>12862.75694</v>
+        <v>12864.01544</v>
       </c>
       <c r="P47" t="b">
         <v>0</v>
@@ -6142,7 +6225,7 @@
         <v>45597</v>
       </c>
       <c r="B48" t="n">
-        <v>6361.1</v>
+        <v>6362.3</v>
       </c>
       <c r="C48" t="n">
         <v>298.7</v>
@@ -6151,7 +6234,7 @@
         <v>98.5</v>
       </c>
       <c r="E48" t="n">
-        <v>7212.7</v>
+        <v>7222.2</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -6163,22 +6246,22 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>238.4</v>
+        <v>238.2</v>
       </c>
       <c r="J48" t="n">
         <v>353.8</v>
       </c>
       <c r="K48" t="n">
-        <v>17577.9</v>
+        <v>17588.4</v>
       </c>
       <c r="L48" t="n">
         <v>6501.7</v>
       </c>
       <c r="N48" t="n">
-        <v>6651.146189999999</v>
+        <v>6655.64349</v>
       </c>
       <c r="O48" t="n">
-        <v>12862.75694</v>
+        <v>12864.01544</v>
       </c>
       <c r="P48" t="b">
         <v>0</v>
@@ -6189,7 +6272,7 @@
         <v>45627</v>
       </c>
       <c r="B49" t="n">
-        <v>6361.2</v>
+        <v>6362.4</v>
       </c>
       <c r="C49" t="n">
         <v>298.7</v>
@@ -6198,7 +6281,7 @@
         <v>98.5</v>
       </c>
       <c r="E49" t="n">
-        <v>7360.3</v>
+        <v>7369.8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -6210,22 +6293,22 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>238.4</v>
+        <v>238.2</v>
       </c>
       <c r="J49" t="n">
         <v>353.8</v>
       </c>
       <c r="K49" t="n">
-        <v>17725.5</v>
+        <v>17736.1</v>
       </c>
       <c r="L49" t="n">
         <v>6501.7</v>
       </c>
       <c r="N49" t="n">
-        <v>6797.09921</v>
+        <v>6801.691559999999</v>
       </c>
       <c r="O49" t="n">
-        <v>12862.83094</v>
+        <v>12864.08944</v>
       </c>
       <c r="P49" t="b">
         <v>0</v>
@@ -6236,7 +6319,7 @@
         <v>45658</v>
       </c>
       <c r="B50" t="n">
-        <v>6361.2</v>
+        <v>6362.4</v>
       </c>
       <c r="C50" t="n">
         <v>298.7</v>
@@ -6245,7 +6328,7 @@
         <v>98.5</v>
       </c>
       <c r="E50" t="n">
-        <v>7492.9</v>
+        <v>7503.2</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -6257,22 +6340,22 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>238.7</v>
+        <v>238.5</v>
       </c>
       <c r="J50" t="n">
         <v>353.8</v>
       </c>
       <c r="K50" t="n">
-        <v>17858.4</v>
+        <v>17869.7</v>
       </c>
       <c r="L50" t="n">
         <v>6501.7</v>
       </c>
       <c r="N50" t="n">
-        <v>6928.3334</v>
+        <v>6933.62432</v>
       </c>
       <c r="O50" t="n">
-        <v>12862.83094</v>
+        <v>12864.08944</v>
       </c>
       <c r="P50" t="b">
         <v>0</v>
@@ -6283,7 +6366,7 @@
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>6361.2</v>
+        <v>6362.4</v>
       </c>
       <c r="C51" t="n">
         <v>298.7</v>
@@ -6292,7 +6375,7 @@
         <v>98.5</v>
       </c>
       <c r="E51" t="n">
-        <v>7563.4</v>
+        <v>7574.2</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -6304,22 +6387,22 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>239.1</v>
+        <v>238.9</v>
       </c>
       <c r="J51" t="n">
         <v>353.8</v>
       </c>
       <c r="K51" t="n">
-        <v>17929.4</v>
+        <v>17941.2</v>
       </c>
       <c r="L51" t="n">
         <v>6501.7</v>
       </c>
       <c r="N51" t="n">
-        <v>6998.57849</v>
+        <v>7004.36201</v>
       </c>
       <c r="O51" t="n">
-        <v>12862.86094</v>
+        <v>12864.11944</v>
       </c>
       <c r="P51" t="b">
         <v>0</v>
@@ -6330,7 +6413,7 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>6361.2</v>
+        <v>6362.4</v>
       </c>
       <c r="C52" t="n">
         <v>298.7</v>
@@ -6339,7 +6422,7 @@
         <v>98.5</v>
       </c>
       <c r="E52" t="n">
-        <v>7664.3</v>
+        <v>7675.4</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -6351,22 +6434,22 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>239.1</v>
+        <v>238.9</v>
       </c>
       <c r="J52" t="n">
         <v>353.8</v>
       </c>
       <c r="K52" t="n">
-        <v>18030.3</v>
+        <v>18042.4</v>
       </c>
       <c r="L52" t="n">
         <v>6501.7</v>
       </c>
       <c r="N52" t="n">
-        <v>7098.4146</v>
+        <v>7104.51386</v>
       </c>
       <c r="O52" t="n">
-        <v>12862.86094</v>
+        <v>12864.11944</v>
       </c>
       <c r="P52" t="b">
         <v>0</v>
@@ -6377,7 +6460,7 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>6361.5</v>
+        <v>6362.8</v>
       </c>
       <c r="C53" t="n">
         <v>298.7</v>
@@ -6386,7 +6469,7 @@
         <v>98.5</v>
       </c>
       <c r="E53" t="n">
-        <v>7809.6</v>
+        <v>7821.2</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -6398,22 +6481,22 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>239.2</v>
+        <v>239</v>
       </c>
       <c r="J53" t="n">
         <v>353.8</v>
       </c>
       <c r="K53" t="n">
-        <v>18176</v>
+        <v>18188.6</v>
       </c>
       <c r="L53" t="n">
         <v>6501.7</v>
       </c>
       <c r="N53" t="n">
-        <v>7242.93625</v>
+        <v>7249.526170000001</v>
       </c>
       <c r="O53" t="n">
-        <v>12863.20694</v>
+        <v>12864.46544</v>
       </c>
       <c r="P53" t="b">
         <v>0</v>
@@ -6424,7 +6507,7 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>6361.5</v>
+        <v>6362.8</v>
       </c>
       <c r="C54" t="n">
         <v>298.7</v>
@@ -6433,7 +6516,7 @@
         <v>98.5</v>
       </c>
       <c r="E54" t="n">
-        <v>7899.6</v>
+        <v>7911.4</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -6445,22 +6528,22 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>239.4</v>
+        <v>239.2</v>
       </c>
       <c r="J54" t="n">
         <v>353.8</v>
       </c>
       <c r="K54" t="n">
-        <v>18266.2</v>
+        <v>18279</v>
       </c>
       <c r="L54" t="n">
         <v>6501.7</v>
       </c>
       <c r="N54" t="n">
-        <v>7331.721039999999</v>
+        <v>7338.53955</v>
       </c>
       <c r="O54" t="n">
-        <v>12863.20694</v>
+        <v>12864.46544</v>
       </c>
       <c r="P54" t="b">
         <v>0</v>
@@ -6471,7 +6554,7 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>6361.5</v>
+        <v>6362.8</v>
       </c>
       <c r="C55" t="n">
         <v>298.7</v>
@@ -6480,7 +6563,7 @@
         <v>98.5</v>
       </c>
       <c r="E55" t="n">
-        <v>7990.1</v>
+        <v>8002.7</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -6492,22 +6575,22 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>239.6</v>
+        <v>239.4</v>
       </c>
       <c r="J55" t="n">
         <v>353.8</v>
       </c>
       <c r="K55" t="n">
-        <v>18356.9</v>
+        <v>18370.6</v>
       </c>
       <c r="L55" t="n">
         <v>6501.7</v>
       </c>
       <c r="N55" t="n">
-        <v>7421.56555</v>
+        <v>7429.13708</v>
       </c>
       <c r="O55" t="n">
-        <v>12863.20694</v>
+        <v>12864.46544</v>
       </c>
       <c r="P55" t="b">
         <v>0</v>
@@ -6518,7 +6601,7 @@
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>6361.5</v>
+        <v>6362.8</v>
       </c>
       <c r="C56" t="n">
         <v>298.7</v>
@@ -6527,7 +6610,7 @@
         <v>98.5</v>
       </c>
       <c r="E56" t="n">
-        <v>8077.4</v>
+        <v>8090.9</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -6539,22 +6622,22 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>241.2</v>
+        <v>241</v>
       </c>
       <c r="J56" t="n">
         <v>353.8</v>
       </c>
       <c r="K56" t="n">
-        <v>18445.8</v>
+        <v>18460.3</v>
       </c>
       <c r="L56" t="n">
         <v>6501.7</v>
       </c>
       <c r="N56" t="n">
-        <v>7507.99119</v>
+        <v>7516.48803</v>
       </c>
       <c r="O56" t="n">
-        <v>12863.20694</v>
+        <v>12864.46544</v>
       </c>
       <c r="P56" t="b">
         <v>0</v>
@@ -6565,7 +6648,7 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>6361.5</v>
+        <v>6362.8</v>
       </c>
       <c r="C57" t="n">
         <v>298.7</v>
@@ -6574,7 +6657,7 @@
         <v>98.5</v>
       </c>
       <c r="E57" t="n">
-        <v>8179.5</v>
+        <v>8194</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -6592,16 +6675,16 @@
         <v>353.8</v>
       </c>
       <c r="K57" t="n">
-        <v>18547.9</v>
+        <v>18563.6</v>
       </c>
       <c r="L57" t="n">
         <v>6501.7</v>
       </c>
       <c r="N57" t="n">
-        <v>7609.600310000001</v>
+        <v>7619.11166</v>
       </c>
       <c r="O57" t="n">
-        <v>12863.20694</v>
+        <v>12864.46544</v>
       </c>
       <c r="P57" t="b">
         <v>0</v>
@@ -6612,7 +6695,7 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>6361.5</v>
+        <v>6362.8</v>
       </c>
       <c r="C58" t="n">
         <v>298.7</v>
@@ -6621,7 +6704,7 @@
         <v>98.5</v>
       </c>
       <c r="E58" t="n">
-        <v>8256.799999999999</v>
+        <v>8272.799999999999</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -6639,16 +6722,16 @@
         <v>353.8</v>
       </c>
       <c r="K58" t="n">
-        <v>18626</v>
+        <v>18643.2</v>
       </c>
       <c r="L58" t="n">
         <v>6501.7</v>
       </c>
       <c r="N58" t="n">
-        <v>7686.83933</v>
+        <v>7697.840870000001</v>
       </c>
       <c r="O58" t="n">
-        <v>12863.20694</v>
+        <v>12864.46544</v>
       </c>
       <c r="P58" t="b">
         <v>0</v>
@@ -6659,7 +6742,7 @@
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>6372.9</v>
+        <v>6374.2</v>
       </c>
       <c r="C59" t="n">
         <v>298.7</v>
@@ -6668,7 +6751,7 @@
         <v>98.5</v>
       </c>
       <c r="E59" t="n">
-        <v>8349.799999999999</v>
+        <v>8367.4</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -6686,16 +6769,16 @@
         <v>353.8</v>
       </c>
       <c r="K59" t="n">
-        <v>18730.7</v>
+        <v>18749.5</v>
       </c>
       <c r="L59" t="n">
         <v>6501.7</v>
       </c>
       <c r="N59" t="n">
-        <v>7779.860559999998</v>
+        <v>7792.396479999999</v>
       </c>
       <c r="O59" t="n">
-        <v>12874.60694</v>
+        <v>12875.86544</v>
       </c>
       <c r="P59" t="b">
         <v>0</v>
@@ -6706,7 +6789,7 @@
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>6374.1</v>
+        <v>6375.4</v>
       </c>
       <c r="C60" t="n">
         <v>298.7</v>
@@ -6715,7 +6798,7 @@
         <v>107.7</v>
       </c>
       <c r="E60" t="n">
-        <v>8440</v>
+        <v>8460.200000000001</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -6733,16 +6816,16 @@
         <v>353.8</v>
       </c>
       <c r="K60" t="n">
-        <v>18831.3</v>
+        <v>18852.9</v>
       </c>
       <c r="L60" t="n">
         <v>6501.7</v>
       </c>
       <c r="N60" t="n">
-        <v>7869.78686</v>
+        <v>7885.04786</v>
       </c>
       <c r="O60" t="n">
-        <v>12875.79594</v>
+        <v>12877.05444</v>
       </c>
       <c r="P60" t="b">
         <v>0</v>
@@ -6753,7 +6836,7 @@
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>6374.1</v>
+        <v>6375.4</v>
       </c>
       <c r="C61" t="n">
         <v>298.7</v>
@@ -6762,7 +6845,7 @@
         <v>109.7</v>
       </c>
       <c r="E61" t="n">
-        <v>8528.700000000001</v>
+        <v>8550.700000000001</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -6774,22 +6857,22 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>242.5</v>
+        <v>242.4</v>
       </c>
       <c r="J61" t="n">
         <v>353.8</v>
       </c>
       <c r="K61" t="n">
-        <v>18922.2</v>
+        <v>18945.3</v>
       </c>
       <c r="L61" t="n">
         <v>6501.7</v>
       </c>
       <c r="N61" t="n">
-        <v>7958.310369999999</v>
+        <v>7975.228150000001</v>
       </c>
       <c r="O61" t="n">
-        <v>12875.80594</v>
+        <v>12877.06444</v>
       </c>
       <c r="P61" t="b">
         <v>0</v>
@@ -6800,7 +6883,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>6374.1</v>
+        <v>6375.4</v>
       </c>
       <c r="C62" t="n">
         <v>298.7</v>
@@ -6809,7 +6892,7 @@
         <v>109.7</v>
       </c>
       <c r="E62" t="n">
-        <v>8606</v>
+        <v>8631.1</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -6821,22 +6904,22 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>243.9</v>
+        <v>243.8</v>
       </c>
       <c r="J62" t="n">
         <v>353.8</v>
       </c>
       <c r="K62" t="n">
-        <v>19000.8</v>
+        <v>19027.2</v>
       </c>
       <c r="L62" t="n">
         <v>6501.7</v>
       </c>
       <c r="N62" t="n">
-        <v>8035.418300000001</v>
+        <v>8055.527939999999</v>
       </c>
       <c r="O62" t="n">
-        <v>12875.80594</v>
+        <v>12877.06444</v>
       </c>
       <c r="P62" t="b">
         <v>0</v>
@@ -6847,7 +6930,7 @@
         <v>46054</v>
       </c>
       <c r="B63" t="n">
-        <v>6374.1</v>
+        <v>6375.4</v>
       </c>
       <c r="C63" t="n">
         <v>298.7</v>
@@ -6856,7 +6939,7 @@
         <v>109.7</v>
       </c>
       <c r="E63" t="n">
-        <v>8647.1</v>
+        <v>8674.1</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -6874,16 +6957,16 @@
         <v>353.8</v>
       </c>
       <c r="K63" t="n">
-        <v>19041.9</v>
+        <v>19070.2</v>
       </c>
       <c r="L63" t="n">
         <v>6501.7</v>
       </c>
       <c r="N63" t="n">
-        <v>8076.38571</v>
+        <v>8098.39264</v>
       </c>
       <c r="O63" t="n">
-        <v>12875.80594</v>
+        <v>12877.06444</v>
       </c>
       <c r="P63" t="b">
         <v>0</v>
@@ -6894,7 +6977,7 @@
         <v>46082</v>
       </c>
       <c r="B64" t="n">
-        <v>6374.1</v>
+        <v>6375.4</v>
       </c>
       <c r="C64" t="n">
         <v>298.7</v>
@@ -6903,7 +6986,7 @@
         <v>109.7</v>
       </c>
       <c r="E64" t="n">
-        <v>8688</v>
+        <v>8719.299999999999</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -6921,16 +7004,16 @@
         <v>353.8</v>
       </c>
       <c r="K64" t="n">
-        <v>19082.9</v>
+        <v>19115.4</v>
       </c>
       <c r="L64" t="n">
         <v>6501.7</v>
       </c>
       <c r="N64" t="n">
-        <v>8117.342300000001</v>
+        <v>8143.581379999999</v>
       </c>
       <c r="O64" t="n">
-        <v>12875.80594</v>
+        <v>12877.06444</v>
       </c>
       <c r="P64" t="b">
         <v>0</v>
@@ -6941,7 +7024,7 @@
         <v>46113</v>
       </c>
       <c r="B65" t="n">
-        <v>6374.1</v>
+        <v>6375.4</v>
       </c>
       <c r="C65" t="n">
         <v>298.7</v>
@@ -6950,7 +7033,7 @@
         <v>109.7</v>
       </c>
       <c r="E65" t="n">
-        <v>8750.1</v>
+        <v>8789.700000000001</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -6962,22 +7045,22 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>244.2</v>
+        <v>244.1</v>
       </c>
       <c r="J65" t="n">
         <v>353.8</v>
       </c>
       <c r="K65" t="n">
-        <v>19145.3</v>
+        <v>19186</v>
       </c>
       <c r="L65" t="n">
         <v>6501.7</v>
       </c>
       <c r="N65" t="n">
-        <v>8179.42578</v>
+        <v>8213.950209999999</v>
       </c>
       <c r="O65" t="n">
-        <v>12875.80594</v>
+        <v>12877.06444</v>
       </c>
       <c r="P65" t="b">
         <v>0</v>
@@ -6988,7 +7071,7 @@
         <v>46143</v>
       </c>
       <c r="B66" t="n">
-        <v>6374.1</v>
+        <v>6375.4</v>
       </c>
       <c r="C66" t="n">
         <v>298.7</v>
@@ -6997,7 +7080,7 @@
         <v>109.7</v>
       </c>
       <c r="E66" t="n">
-        <v>8787.799999999999</v>
+        <v>8837.299999999999</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -7015,16 +7098,16 @@
         <v>353.8</v>
       </c>
       <c r="K66" t="n">
-        <v>19183.4</v>
+        <v>19234.1</v>
       </c>
       <c r="L66" t="n">
         <v>6501.7</v>
       </c>
       <c r="N66" t="n">
-        <v>8217.06524</v>
+        <v>8261.593340000001</v>
       </c>
       <c r="O66" t="n">
-        <v>12875.80594</v>
+        <v>12877.06444</v>
       </c>
       <c r="P66" t="b">
         <v>0</v>
@@ -7035,7 +7118,7 @@
         <v>46174</v>
       </c>
       <c r="B67" t="n">
-        <v>6374.1</v>
+        <v>6375.4</v>
       </c>
       <c r="C67" t="n">
         <v>298.7</v>
@@ -7044,7 +7127,7 @@
         <v>109.7</v>
       </c>
       <c r="E67" t="n">
-        <v>8808.5</v>
+        <v>8865.9</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -7056,25 +7139,25 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>244.8</v>
+        <v>244.7</v>
       </c>
       <c r="J67" t="n">
         <v>353.8</v>
       </c>
       <c r="K67" t="n">
-        <v>19204.2</v>
+        <v>19262.9</v>
       </c>
       <c r="L67" t="n">
         <v>6501.7</v>
       </c>
       <c r="N67" t="n">
-        <v>8237.77411</v>
+        <v>8290.160389999999</v>
       </c>
       <c r="O67" t="n">
-        <v>12875.80594</v>
+        <v>12877.06444</v>
       </c>
       <c r="P67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -7082,7 +7165,7 @@
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>6374.1</v>
+        <v>6375.4</v>
       </c>
       <c r="C68" t="n">
         <v>298.7</v>
@@ -7091,7 +7174,7 @@
         <v>109.7</v>
       </c>
       <c r="E68" t="n">
-        <v>8824.700000000001</v>
+        <v>8897.6</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -7109,19 +7192,19 @@
         <v>353.8</v>
       </c>
       <c r="K68" t="n">
-        <v>19220.5</v>
+        <v>19294.7</v>
       </c>
       <c r="L68" t="n">
         <v>6501.7</v>
       </c>
       <c r="N68" t="n">
-        <v>8253.96033</v>
+        <v>8321.84015</v>
       </c>
       <c r="O68" t="n">
-        <v>12875.80594</v>
+        <v>12877.06444</v>
       </c>
       <c r="P68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -7129,7 +7212,7 @@
         <v>46235</v>
       </c>
       <c r="B69" t="n">
-        <v>6374.1</v>
+        <v>6375.4</v>
       </c>
       <c r="C69" t="n">
         <v>298.7</v>
@@ -7138,7 +7221,7 @@
         <v>109.7</v>
       </c>
       <c r="E69" t="n">
-        <v>8829.200000000001</v>
+        <v>8909.1</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -7150,24 +7233,118 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>244.9</v>
+        <v>245</v>
       </c>
       <c r="J69" t="n">
         <v>353.8</v>
       </c>
       <c r="K69" t="n">
-        <v>19225</v>
+        <v>19306.3</v>
       </c>
       <c r="L69" t="n">
         <v>6501.7</v>
       </c>
       <c r="N69" t="n">
-        <v>8258.501559999999</v>
+        <v>8333.32777</v>
       </c>
       <c r="O69" t="n">
-        <v>12875.80594</v>
+        <v>12877.06444</v>
       </c>
       <c r="P69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>6375.4</v>
+      </c>
+      <c r="C70" t="n">
+        <v>298.7</v>
+      </c>
+      <c r="D70" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="E70" t="n">
+        <v>8910.6</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3014.6</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>245</v>
+      </c>
+      <c r="J70" t="n">
+        <v>353.8</v>
+      </c>
+      <c r="K70" t="n">
+        <v>19307.8</v>
+      </c>
+      <c r="L70" t="n">
+        <v>6501.7</v>
+      </c>
+      <c r="N70" t="n">
+        <v>8334.829009999999</v>
+      </c>
+      <c r="O70" t="n">
+        <v>12877.06444</v>
+      </c>
+      <c r="P70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B71" t="n">
+        <v>6375.4</v>
+      </c>
+      <c r="C71" t="n">
+        <v>298.7</v>
+      </c>
+      <c r="D71" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="E71" t="n">
+        <v>8911.200000000001</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3014.6</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>245</v>
+      </c>
+      <c r="J71" t="n">
+        <v>353.8</v>
+      </c>
+      <c r="K71" t="n">
+        <v>19308.4</v>
+      </c>
+      <c r="L71" t="n">
+        <v>6501.7</v>
+      </c>
+      <c r="N71" t="n">
+        <v>8335.43381</v>
+      </c>
+      <c r="O71" t="n">
+        <v>12877.06444</v>
+      </c>
+      <c r="P71" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7227,16 +7404,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6268.2</v>
+        <v>6269.5</v>
       </c>
       <c r="D2" t="n">
         <v>6192</v>
       </c>
       <c r="E2" t="n">
-        <v>76.2</v>
+        <v>77.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="3">
@@ -7293,16 +7470,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6287.6</v>
+        <v>6288.9</v>
       </c>
       <c r="D5" t="n">
         <v>6192</v>
       </c>
       <c r="E5" t="n">
-        <v>95.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="6">
@@ -7359,16 +7536,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6299.5</v>
+        <v>6300.7</v>
       </c>
       <c r="D8" t="n">
         <v>6192</v>
       </c>
       <c r="E8" t="n">
-        <v>107.5</v>
+        <v>108.7</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -7425,13 +7602,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6314.3</v>
+        <v>6315.6</v>
       </c>
       <c r="D11" t="n">
         <v>6406</v>
       </c>
       <c r="E11" t="n">
-        <v>-91.7</v>
+        <v>-90.40000000000001</v>
       </c>
       <c r="F11" t="n">
         <v>-1.4</v>
@@ -7491,13 +7668,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6361.2</v>
+        <v>6362.4</v>
       </c>
       <c r="D14" t="n">
         <v>6412</v>
       </c>
       <c r="E14" t="n">
-        <v>-50.8</v>
+        <v>-49.6</v>
       </c>
       <c r="F14" t="n">
         <v>-0.8</v>
@@ -7557,13 +7734,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6374.1</v>
+        <v>6375.4</v>
       </c>
       <c r="D17" t="n">
         <v>6431</v>
       </c>
       <c r="E17" t="n">
-        <v>-56.9</v>
+        <v>-55.6</v>
       </c>
       <c r="F17" t="n">
         <v>-0.9</v>
@@ -7624,123 +7801,303 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>asof_utc</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>register_last_modified</t>
+          <t>series</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>latest_start_date</t>
+          <t>this_file_MW</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>plants</t>
+          <t>Ember_year_end_MW</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Hydro_MW</t>
+          <t>difference_MW</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>PumpedStorage_MW</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+          <t>difference_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2934.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Wind_MW</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="C3" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-6.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Solar_MW</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Nuclear_MW</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Gas_MW</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Bioenergy_MW</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Other_MW</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>row_date</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:13 UTC</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Mon, 14 Sep 2026 11:42:19 GMT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>339499</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6374.1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>6501.7</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="C4" t="n">
+        <v>3505.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3520</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>90</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-6.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4286.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4530</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-243.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-5.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>90</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-6.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5833.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6060</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-226.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-6.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>7503.2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7760</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-256.8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8631.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9110</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-478.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-5.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>109.7</v>
       </c>
-      <c r="H2" t="n">
-        <v>8829.200000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3014.6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>298.7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>244.9</v>
-      </c>
-      <c r="L2" t="n">
-        <v>353.8</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
+      <c r="D13" t="n">
+        <v>110</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -7754,6 +8111,185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>asof_utc</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>register_last_modified</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>latest_start_date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>plants</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Hydro_MW</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>PumpedStorage_MW</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Nuclear_MW</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Gas_MW</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Bioenergy_MW</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Other_MW</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>row_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-12 04:13 UTC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 11:42:19 GMT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>339499</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6374.1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6501.7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8829.200000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3014.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>298.7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>244.9</v>
+      </c>
+      <c r="L2" t="n">
+        <v>353.8</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-28 01:17 UTC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 20:13:05 GMT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>341981</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6375.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6501.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8911.200000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3014.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>298.7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>245</v>
+      </c>
+      <c r="L3" t="n">
+        <v>353.8</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -7787,17 +8323,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-28 01:17 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Last-Modified Mon, 14 Sep 2026 11:42:19 GMT; ETag "70295f540bd344db40fc81755b780e02-3"; size 19195387</t>
+          <t>Last-Modified Thu, 15 Oct 2026 20:13:05 GMT; ETag "7f13e889b71aca7c32c1e2c5b57dee69-3"; size 19732226</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8f207b57a5df548a78c587ba1e6a732549b1b16525d9b07db2f2a1d63c1cb2c6</t>
+          <t>e803c67fbccce84533b36e13cb39c85c102325ff0587abcb4374b23b41d42a72</t>
         </is>
       </c>
     </row>
